--- a/downloads/base_interactiva_pendientes.xlsx
+++ b/downloads/base_interactiva_pendientes.xlsx
@@ -356,7 +356,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AB20"/>
+  <dimension ref="A1:AB19"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="21" max="21" width="20.7109375" style="2" customWidth="1"/>
@@ -1371,52 +1371,52 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Mega</t>
+          <t>Minera Agua Rica (MARA)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Ampliación de la capacidad de procesamiento, fraccionamiento y transporte de líquidos del gas natural provenientes de la Cuenca Neuquina. Las obras abarcan instalaciones en Neuquén y el corredor de transporte hasta el complejo de fraccionamiento y exportación de Bahía Blanca, con un aumento proyectado de 1.500 toneladas diarias.</t>
+          <t>Desarrollo de una mina de cobre, oro, plata y molibdeno en Catamarca, integrando el yacimiento Agua Rica con la infraestructura existente de Alumbrera, ubicada a unos 35 km. El esquema MARA contempla explotación, procesamiento y uso de instalaciones compartidas para producción destinada principalmente a exportación.</t>
         </is>
       </c>
       <c r="D14">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>YPF S.A. (Argentina); Petrobras (Brasil); Dow (Argentina)</t>
+          <t>Glencore (Suiza)</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Compañía Mega S.A. – Sucursal Dedicada</t>
+          <t>Minera Agua Rica LLC Sucursal Argentina</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Petróleo y Gas</t>
+          <t>Minería</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Midstream</t>
+          <t>Cobre</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>Neuquén; Río Negro; La Pampa; Buenos Aires</t>
+          <t>Catamarca</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>Múltiples</t>
+          <t>NOA</t>
         </is>
       </c>
       <c r="M14">
-        <v>360</v>
+        <v>4000</v>
       </c>
       <c r="N14">
-        <v>360</v>
+        <v>4000</v>
       </c>
       <c r="R14">
         <v>0</v>
@@ -1427,68 +1427,68 @@
         </is>
       </c>
       <c r="V14" s="2">
-        <v>46099</v>
+        <v>45887</v>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>Globaris; EconoJournal; Compañía MEGA; Luis Caputo; auditoría 2026-08-08</t>
+          <t>Globaris; Glencore; Luis Caputo; Reuters; Infobae; auditoría 2026-08-08</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>https://econojournal.com.ar/oilgas/vaca-muerta-mega-se-presenta-al-rigi-con-una-inversion-de-us360-millones-en-su-planta-de-separacion-de-liquidos-del-gas/; https://www.ingenierowhite.com/2026/07/31/mega-obtuvo-la-aprobacion-de-su-proyecto-de-inversion-bajo-el-rigi/; https://x.com/LuisCaputoAR/status/2083255389399744911</t>
+          <t>https://www.glencore.com/media-and-insights/news/glencore-submits-RIGI-applications-in-respect-of-its-argentine-copper-projects; https://x.com/LuisCaputoAR/status/1957458679835594969; https://www.reuters.com/latam/negocio/7X5ZW2SXG5IYNBUILMTT6GMS6U-2025-08-21/; https://www.infobae.com/economia/2026/05/13/el-gobierno-aprobo-el-ingreso-al-rigi-de-la-ampliacion-del-gasoducto-perito-moreno-con-una-inversion-de-usd-550-millones/</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Minera Agua Rica (MARA)</t>
+          <t>Fértil Pampa</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Desarrollo de una mina de cobre, oro, plata y molibdeno en Catamarca, integrando el yacimiento Agua Rica con la infraestructura existente de Alumbrera, ubicada a unos 35 km. El esquema MARA contempla explotación, procesamiento y uso de instalaciones compartidas para producción destinada principalmente a exportación.</t>
+          <t>Construcción de un complejo industrial de amoníaco y urea granulada en Bahía Blanca, provincia de Buenos Aires, a cargo de Fértil Pampa. La planta tendrá dos trenes de urea, instalaciones auxiliares, almacenamiento y logística portuaria, con capacidad prevista de 2,1 millones de toneladas anuales.</t>
         </is>
       </c>
       <c r="D15">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Glencore (Suiza)</t>
+          <t>Pampa Energía (Argentina)</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Minera Agua Rica LLC Sucursal Argentina</t>
+          <t>Fértil Pampa S.A.U.</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Minería</t>
+          <t>Petróleo y Gas</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Cobre</t>
+          <t>Petroquímica / Fertilizantes</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>Catamarca</t>
+          <t>Buenos Aires</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>NOA</t>
+          <t>Centro</t>
         </is>
       </c>
       <c r="M15">
-        <v>4000</v>
+        <v>2400</v>
       </c>
       <c r="N15">
-        <v>4000</v>
+        <v>2400</v>
       </c>
       <c r="R15">
         <v>0</v>
@@ -1499,68 +1499,68 @@
         </is>
       </c>
       <c r="V15" s="2">
-        <v>45887</v>
+        <v>46136</v>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>Globaris; Glencore; Luis Caputo; Reuters; Infobae; auditoría 2026-08-08</t>
+          <t>Globaris; Pampa Energía; International Finance Corporation; El Cronista; La Nación; Luis Caputo; auditoría 2026-08-08</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>https://www.glencore.com/media-and-insights/news/glencore-submits-RIGI-applications-in-respect-of-its-argentine-copper-projects; https://x.com/LuisCaputoAR/status/1957458679835594969; https://www.reuters.com/latam/negocio/7X5ZW2SXG5IYNBUILMTT6GMS6U-2025-08-21/; https://www.infobae.com/economia/2026/05/13/el-gobierno-aprobo-el-ingreso-al-rigi-de-la-ampliacion-del-gasoducto-perito-moreno-con-una-inversion-de-usd-550-millones/</t>
+          <t>https://ri.pampa.com/en/press-release/pampa-energia-announces-its-entry-into-the-fertilizer-business-with-the-construction-of-latin-americas-largest-urea-plant/; https://disclosures.ifc.org/project-detail/ED/52106/fer-il-p; https://www.cronista.com/negocios/fertil-pampa-se-presenta-al-rigi-con-una-inversion-de-us-2400-millones-para-producir-fertilizantes/; https://www.lanacion.com.ar/economia/campo/invertiria-us2400-millones-una-empresa-de-marcelo-mindlin-pidio-ingresar-al-rigi-para-producir-nid23042026/</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Fértil Pampa</t>
+          <t>Jama Solaroz</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Construcción de un complejo industrial de amoníaco y urea granulada en Bahía Blanca, provincia de Buenos Aires, a cargo de Fértil Pampa. La planta tendrá dos trenes de urea, instalaciones auxiliares, almacenamiento y logística portuaria, con capacidad prevista de 2,1 millones de toneladas anuales.</t>
+          <t>Desarrollo integrado de litio en los proyectos Jama y Solaroz, en la Puna de Jujuy, con una planta prevista en el Salar de Jama. La iniciativa contempla extracción de salmuera y producción de compuestos de litio, con una capacidad informada de aproximadamente 22.000 toneladas anuales.</t>
         </is>
       </c>
       <c r="D16">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Pampa Energía (Argentina)</t>
+          <t>CNGR Advanced Material Co., Ltd. (China)</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Fértil Pampa S.A.U.</t>
+          <t>CNGR Advanced Material Co., Ltd.</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Petróleo y Gas</t>
+          <t>Minería</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Petroquímica / Fertilizantes</t>
+          <t>Litio</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>Buenos Aires</t>
+          <t>Jujuy</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>Centro</t>
+          <t>NOA</t>
         </is>
       </c>
       <c r="M16">
-        <v>2400</v>
+        <v>1151</v>
       </c>
       <c r="N16">
-        <v>2400</v>
+        <v>1151</v>
       </c>
       <c r="R16">
         <v>0</v>
@@ -1571,68 +1571,68 @@
         </is>
       </c>
       <c r="V16" s="2">
-        <v>46136</v>
+        <v>46111</v>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>Globaris; Pampa Energía; International Finance Corporation; El Cronista; La Nación; Luis Caputo; auditoría 2026-08-08</t>
+          <t>Globaris; Gobierno de Jujuy; El Tribuno de Jujuy; Infobae; auditoría 2026-08-08</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>https://ri.pampa.com/en/press-release/pampa-energia-announces-its-entry-into-the-fertilizer-business-with-the-construction-of-latin-americas-largest-urea-plant/; https://disclosures.ifc.org/project-detail/ED/52106/fer-il-p; https://www.cronista.com/negocios/fertil-pampa-se-presenta-al-rigi-con-una-inversion-de-us-2400-millones-para-producir-fertilizantes/; https://www.lanacion.com.ar/economia/campo/invertiria-us2400-millones-una-empresa-de-marcelo-mindlin-pidio-ingresar-al-rigi-para-producir-nid23042026/</t>
+          <t>https://prensa.jujuy.gob.ar/jujuy/jujuy-se-afianza-como-productor-minerales-criticos-el-desarrollo-la-transicion-energetica-n120116; https://eltribunodejujuy.com/informacion-general/2026-4-1-0-0-0-proyecto-de-litio-en-jujuy-busca-la-adhesion-al-rigi; https://www.infobae.com/economia/2026/05/13/el-gobierno-aprobo-el-ingreso-al-rigi-de-la-ampliacion-del-gasoducto-perito-moreno-con-una-inversion-de-usd-550-millones/</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Jama Solaroz</t>
+          <t>LLL Oil</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Desarrollo integrado de litio en los proyectos Jama y Solaroz, en la Puna de Jujuy, con una planta prevista en el Salar de Jama. La iniciativa contempla extracción de salmuera y producción de compuestos de litio, con una capacidad informada de aproximadamente 22.000 toneladas anuales.</t>
+          <t>Desarrollo integrado de cinco bloques contiguos de petróleo no convencional en Vaca Muerta: La Angostura Norte, La Angostura Sur I, La Angostura Sur II, La Angostura Suroeste y Barreal Grande. El programa prevé perforar 1.152 pozos y compartir instalaciones de superficie y servicios para alcanzar una producción aproximada de 240.000 barriles diarios hacia 2032, destinada a exportación.</t>
         </is>
       </c>
       <c r="D17">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>CNGR Advanced Material Co., Ltd. (China)</t>
+          <t>YPF S.A. (Argentina)</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>CNGR Advanced Material Co., Ltd.</t>
+          <t>YPF</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Minería</t>
+          <t>Petróleo y Gas</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Litio</t>
+          <t>Upstream</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>Jujuy</t>
+          <t>Neuquén</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>NOA</t>
+          <t>Patagonia</t>
         </is>
       </c>
       <c r="M17">
-        <v>1151</v>
+        <v>25000</v>
       </c>
       <c r="N17">
-        <v>1151</v>
+        <v>25000</v>
       </c>
       <c r="R17">
         <v>0</v>
@@ -1643,41 +1643,41 @@
         </is>
       </c>
       <c r="V17" s="2">
-        <v>46111</v>
+        <v>46157</v>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>Globaris; Gobierno de Jujuy; El Tribuno de Jujuy; Infobae; auditoría 2026-08-08</t>
+          <t>Globaris; YPF; EconoJournal; Reuters; auditoría 2026-08-08</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>https://prensa.jujuy.gob.ar/jujuy/jujuy-se-afianza-como-productor-minerales-criticos-el-desarrollo-la-transicion-energetica-n120116; https://eltribunodejujuy.com/informacion-general/2026-4-1-0-0-0-proyecto-de-litio-en-jujuy-busca-la-adhesion-al-rigi; https://www.infobae.com/economia/2026/05/13/el-gobierno-aprobo-el-ingreso-al-rigi-de-la-ampliacion-del-gasoducto-perito-moreno-con-una-inversion-de-usd-550-millones/</t>
+          <t>https://www.instagram.com/p/DYX1JXjj-bC/; https://econojournal.com.ar/destacada/ypf-presento-rigi-acelerar-produccion-petroleo-vaca-muerta/; https://www.reuters.com/business/energy/argentinas-ypf-registers-25-bln-oil-project-rigi-investment-scheme-2026-05-15/</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>LLL Oil</t>
+          <t>Bandurria Norte</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Desarrollo integrado de cinco bloques contiguos de petróleo no convencional en Vaca Muerta: La Angostura Norte, La Angostura Sur I, La Angostura Sur II, La Angostura Suroeste y Barreal Grande. El programa prevé perforar 1.152 pozos y compartir instalaciones de superficie y servicios para alcanzar una producción aproximada de 240.000 barriles diarios hacia 2032, destinada a exportación.</t>
+          <t>Desarrollo greenfield de petróleo no convencional en Bandurria Norte, Vaca Muerta, sobre una superficie aproximada de 26.500 acres. El plan contempla 332 pozos horizontales, planta de tratamiento de crudo, compresión de gas, redes de recolección y ductos, con una meta de 50.000 barriles equivalentes diarios.</t>
         </is>
       </c>
       <c r="D18">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>YPF S.A. (Argentina)</t>
+          <t>Vista Energy (Argentina)</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>YPF</t>
+          <t>Vista Energy</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1701,10 +1701,10 @@
         </is>
       </c>
       <c r="M18">
-        <v>25000</v>
+        <v>5800</v>
       </c>
       <c r="N18">
-        <v>25000</v>
+        <v>5800</v>
       </c>
       <c r="R18">
         <v>0</v>
@@ -1715,41 +1715,41 @@
         </is>
       </c>
       <c r="V18" s="2">
-        <v>46157</v>
+        <v>46224</v>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>Globaris; YPF; EconoJournal; Reuters; auditoría 2026-08-08</t>
+          <t>Globaris; EconoJournal; Vista Energy / SEC; Oil &amp; Gas Journal; auditoría 2026-08-08</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DYX1JXjj-bC/; https://econojournal.com.ar/destacada/ypf-presento-rigi-acelerar-produccion-petroleo-vaca-muerta/; https://www.reuters.com/business/energy/argentinas-ypf-registers-25-bln-oil-project-rigi-investment-scheme-2026-05-15/</t>
+          <t>https://econojournal.com.ar/oilgas/vista-energy-pidio-la-adhesion-al-rigi-para-un-proyecto-de-us-5-800-millones-en-vaca-muerta/; https://www.sec.gov/Archives/edgar/data/1762506/000119312526306139/d151775dex1.htm; https://www.ogj.com/exploration-development/news/55394130/vista-seeks-rigi-approval-for-58-billion-bandurria-norte-development</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Bandurria Norte</t>
+          <t>Argentina LNG</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Desarrollo greenfield de petróleo no convencional en Bandurria Norte, Vaca Muerta, sobre una superficie aproximada de 26.500 acres. El plan contempla 332 pozos horizontales, planta de tratamiento de crudo, compresión de gas, redes de recolección y ductos, con una meta de 50.000 barriles equivalentes diarios.</t>
+          <t>Proyecto integrado de producción y exportación de gas natural licuado: desarrollo de gas rico en Vaca Muerta, infraestructura dedicada de transporte, plantas de procesamiento y fraccionamiento y dos unidades flotantes de licuefacción (FLNG) por 12 MTPA en el Golfo San Matías.</t>
         </is>
       </c>
       <c r="D19">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Vista Energy (Argentina)</t>
+          <t>YPF S.A. (Argentina); Eni S.p.A. (Italia); XRG (Emiratos Árabes Unidos)</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vista Energy</t>
+          <t>YPF</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1759,12 +1759,12 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Upstream</t>
+          <t>Midstream</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>Neuquén</t>
+          <t>Neuquén; Río Negro</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -1773,10 +1773,7 @@
         </is>
       </c>
       <c r="M19">
-        <v>5800</v>
-      </c>
-      <c r="N19">
-        <v>5800</v>
+        <v>51000</v>
       </c>
       <c r="R19">
         <v>0</v>
@@ -1787,83 +1784,14 @@
         </is>
       </c>
       <c r="V19" s="2">
-        <v>46224</v>
+        <v>46247</v>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>Globaris; EconoJournal; Vista Energy / SEC; Oil &amp; Gas Journal; auditoría 2026-08-08</t>
+          <t>YPF / Argentina LNG; La Nación; Infobae; Data Energía</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
-        <is>
-          <t>https://econojournal.com.ar/oilgas/vista-energy-pidio-la-adhesion-al-rigi-para-un-proyecto-de-us-5-800-millones-en-vaca-muerta/; https://www.sec.gov/Archives/edgar/data/1762506/000119312526306139/d151775dex1.htm; https://www.ogj.com/exploration-development/news/55394130/vista-seeks-rigi-approval-for-58-billion-bandurria-norte-development</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Argentina LNG</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Proyecto integrado de producción y exportación de gas natural licuado: desarrollo de gas rico en Vaca Muerta, infraestructura dedicada de transporte, plantas de procesamiento y fraccionamiento y dos unidades flotantes de licuefacción (FLNG) por 12 MTPA en el Golfo San Matías.</t>
-        </is>
-      </c>
-      <c r="D20">
-        <v>41</v>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>YPF S.A. (Argentina); Eni S.p.A. (Italia); XRG (Emiratos Árabes Unidos)</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>YPF</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>Petróleo y Gas</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>Midstream</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>Neuquén; Río Negro</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>Patagonia</t>
-        </is>
-      </c>
-      <c r="M20">
-        <v>51000</v>
-      </c>
-      <c r="R20">
-        <v>0</v>
-      </c>
-      <c r="S20" t="inlineStr">
-        <is>
-          <t>En evaluación</t>
-        </is>
-      </c>
-      <c r="V20" s="2">
-        <v>46247</v>
-      </c>
-      <c r="AA20" t="inlineStr">
-        <is>
-          <t>YPF / Argentina LNG; La Nación; Infobae; Data Energía</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
         <is>
           <t>https://argentina-lng.ypf.com/assets/pdf/ENG-Argentina-LNG-Adhesion-RIGI.pdf; https://www.lanacion.com.ar/economia/un-proyecto-por-us51000-millones-impulsado-por-ypf-solicito-la-adhesion-al-rigi-nid13082026/; https://www.infobae.com/economia/2026/08/13/con-una-inversion-de-usd-50000-millones-ypf-presenta-al-rigi-el-mayor-proyecto-de-su-historia-para-exportar-gas-de-vaca-muerta/; https://dataenergia.ar/gas/argentina-lgn-solicitaron-la-adhesion-formal-al-rigi-para-una-inversion-historica-de-u-s-51-000-millones-202681319370</t>
         </is>

--- a/downloads/base_interactiva_pendientes.xlsx
+++ b/downloads/base_interactiva_pendientes.xlsx
@@ -356,7 +356,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AB19"/>
+  <dimension ref="A1:AB18"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="21" max="21" width="20.7109375" style="2" customWidth="1"/>
@@ -1443,52 +1443,52 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Fértil Pampa</t>
+          <t>Jama Solaroz</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Construcción de un complejo industrial de amoníaco y urea granulada en Bahía Blanca, provincia de Buenos Aires, a cargo de Fértil Pampa. La planta tendrá dos trenes de urea, instalaciones auxiliares, almacenamiento y logística portuaria, con capacidad prevista de 2,1 millones de toneladas anuales.</t>
+          <t>Desarrollo integrado de litio en los proyectos Jama y Solaroz, en la Puna de Jujuy, con una planta prevista en el Salar de Jama. La iniciativa contempla extracción de salmuera y producción de compuestos de litio, con una capacidad informada de aproximadamente 22.000 toneladas anuales.</t>
         </is>
       </c>
       <c r="D15">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Pampa Energía (Argentina)</t>
+          <t>CNGR Advanced Material Co., Ltd. (China)</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Fértil Pampa S.A.U.</t>
+          <t>CNGR Advanced Material Co., Ltd.</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Petróleo y Gas</t>
+          <t>Minería</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Petroquímica / Fertilizantes</t>
+          <t>Litio</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>Buenos Aires</t>
+          <t>Jujuy</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>Centro</t>
+          <t>NOA</t>
         </is>
       </c>
       <c r="M15">
-        <v>2400</v>
+        <v>1151</v>
       </c>
       <c r="N15">
-        <v>2400</v>
+        <v>1151</v>
       </c>
       <c r="R15">
         <v>0</v>
@@ -1499,68 +1499,68 @@
         </is>
       </c>
       <c r="V15" s="2">
-        <v>46136</v>
+        <v>46111</v>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>Globaris; Pampa Energía; International Finance Corporation; El Cronista; La Nación; Luis Caputo; auditoría 2026-08-08</t>
+          <t>Globaris; Gobierno de Jujuy; El Tribuno de Jujuy; Infobae; auditoría 2026-08-08</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>https://ri.pampa.com/en/press-release/pampa-energia-announces-its-entry-into-the-fertilizer-business-with-the-construction-of-latin-americas-largest-urea-plant/; https://disclosures.ifc.org/project-detail/ED/52106/fer-il-p; https://www.cronista.com/negocios/fertil-pampa-se-presenta-al-rigi-con-una-inversion-de-us-2400-millones-para-producir-fertilizantes/; https://www.lanacion.com.ar/economia/campo/invertiria-us2400-millones-una-empresa-de-marcelo-mindlin-pidio-ingresar-al-rigi-para-producir-nid23042026/</t>
+          <t>https://prensa.jujuy.gob.ar/jujuy/jujuy-se-afianza-como-productor-minerales-criticos-el-desarrollo-la-transicion-energetica-n120116; https://eltribunodejujuy.com/informacion-general/2026-4-1-0-0-0-proyecto-de-litio-en-jujuy-busca-la-adhesion-al-rigi; https://www.infobae.com/economia/2026/05/13/el-gobierno-aprobo-el-ingreso-al-rigi-de-la-ampliacion-del-gasoducto-perito-moreno-con-una-inversion-de-usd-550-millones/</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Jama Solaroz</t>
+          <t>LLL Oil</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Desarrollo integrado de litio en los proyectos Jama y Solaroz, en la Puna de Jujuy, con una planta prevista en el Salar de Jama. La iniciativa contempla extracción de salmuera y producción de compuestos de litio, con una capacidad informada de aproximadamente 22.000 toneladas anuales.</t>
+          <t>Desarrollo integrado de cinco bloques contiguos de petróleo no convencional en Vaca Muerta: La Angostura Norte, La Angostura Sur I, La Angostura Sur II, La Angostura Suroeste y Barreal Grande. El programa prevé perforar 1.152 pozos y compartir instalaciones de superficie y servicios para alcanzar una producción aproximada de 240.000 barriles diarios hacia 2032, destinada a exportación.</t>
         </is>
       </c>
       <c r="D16">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>CNGR Advanced Material Co., Ltd. (China)</t>
+          <t>YPF S.A. (Argentina)</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>CNGR Advanced Material Co., Ltd.</t>
+          <t>YPF</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Minería</t>
+          <t>Petróleo y Gas</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Litio</t>
+          <t>Upstream</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>Jujuy</t>
+          <t>Neuquén</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>NOA</t>
+          <t>Patagonia</t>
         </is>
       </c>
       <c r="M16">
-        <v>1151</v>
+        <v>25000</v>
       </c>
       <c r="N16">
-        <v>1151</v>
+        <v>25000</v>
       </c>
       <c r="R16">
         <v>0</v>
@@ -1571,41 +1571,41 @@
         </is>
       </c>
       <c r="V16" s="2">
-        <v>46111</v>
+        <v>46157</v>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>Globaris; Gobierno de Jujuy; El Tribuno de Jujuy; Infobae; auditoría 2026-08-08</t>
+          <t>Globaris; YPF; EconoJournal; Reuters; auditoría 2026-08-08</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>https://prensa.jujuy.gob.ar/jujuy/jujuy-se-afianza-como-productor-minerales-criticos-el-desarrollo-la-transicion-energetica-n120116; https://eltribunodejujuy.com/informacion-general/2026-4-1-0-0-0-proyecto-de-litio-en-jujuy-busca-la-adhesion-al-rigi; https://www.infobae.com/economia/2026/05/13/el-gobierno-aprobo-el-ingreso-al-rigi-de-la-ampliacion-del-gasoducto-perito-moreno-con-una-inversion-de-usd-550-millones/</t>
+          <t>https://www.instagram.com/p/DYX1JXjj-bC/; https://econojournal.com.ar/destacada/ypf-presento-rigi-acelerar-produccion-petroleo-vaca-muerta/; https://www.reuters.com/business/energy/argentinas-ypf-registers-25-bln-oil-project-rigi-investment-scheme-2026-05-15/</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>LLL Oil</t>
+          <t>Bandurria Norte</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Desarrollo integrado de cinco bloques contiguos de petróleo no convencional en Vaca Muerta: La Angostura Norte, La Angostura Sur I, La Angostura Sur II, La Angostura Suroeste y Barreal Grande. El programa prevé perforar 1.152 pozos y compartir instalaciones de superficie y servicios para alcanzar una producción aproximada de 240.000 barriles diarios hacia 2032, destinada a exportación.</t>
+          <t>Desarrollo greenfield de petróleo no convencional en Bandurria Norte, Vaca Muerta, sobre una superficie aproximada de 26.500 acres. El plan contempla 332 pozos horizontales, planta de tratamiento de crudo, compresión de gas, redes de recolección y ductos, con una meta de 50.000 barriles equivalentes diarios.</t>
         </is>
       </c>
       <c r="D17">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>YPF S.A. (Argentina)</t>
+          <t>Vista Energy (Argentina)</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>YPF</t>
+          <t>Vista Energy</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1629,10 +1629,10 @@
         </is>
       </c>
       <c r="M17">
-        <v>25000</v>
+        <v>5800</v>
       </c>
       <c r="N17">
-        <v>25000</v>
+        <v>5800</v>
       </c>
       <c r="R17">
         <v>0</v>
@@ -1643,41 +1643,41 @@
         </is>
       </c>
       <c r="V17" s="2">
-        <v>46157</v>
+        <v>46224</v>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>Globaris; YPF; EconoJournal; Reuters; auditoría 2026-08-08</t>
+          <t>Globaris; EconoJournal; Vista Energy / SEC; Oil &amp; Gas Journal; auditoría 2026-08-08</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DYX1JXjj-bC/; https://econojournal.com.ar/destacada/ypf-presento-rigi-acelerar-produccion-petroleo-vaca-muerta/; https://www.reuters.com/business/energy/argentinas-ypf-registers-25-bln-oil-project-rigi-investment-scheme-2026-05-15/</t>
+          <t>https://econojournal.com.ar/oilgas/vista-energy-pidio-la-adhesion-al-rigi-para-un-proyecto-de-us-5-800-millones-en-vaca-muerta/; https://www.sec.gov/Archives/edgar/data/1762506/000119312526306139/d151775dex1.htm; https://www.ogj.com/exploration-development/news/55394130/vista-seeks-rigi-approval-for-58-billion-bandurria-norte-development</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Bandurria Norte</t>
+          <t>Argentina LNG</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Desarrollo greenfield de petróleo no convencional en Bandurria Norte, Vaca Muerta, sobre una superficie aproximada de 26.500 acres. El plan contempla 332 pozos horizontales, planta de tratamiento de crudo, compresión de gas, redes de recolección y ductos, con una meta de 50.000 barriles equivalentes diarios.</t>
+          <t>Proyecto integrado de producción y exportación de gas natural licuado: desarrollo de gas rico en Vaca Muerta, infraestructura dedicada de transporte, plantas de procesamiento y fraccionamiento y dos unidades flotantes de licuefacción (FLNG) por 12 MTPA en el Golfo San Matías.</t>
         </is>
       </c>
       <c r="D18">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Vista Energy (Argentina)</t>
+          <t>YPF S.A. (Argentina); Eni S.p.A. (Italia); XRG (Emiratos Árabes Unidos)</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vista Energy</t>
+          <t>YPF</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1687,12 +1687,12 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Upstream</t>
+          <t>Midstream</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>Neuquén</t>
+          <t>Neuquén; Río Negro</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -1701,10 +1701,7 @@
         </is>
       </c>
       <c r="M18">
-        <v>5800</v>
-      </c>
-      <c r="N18">
-        <v>5800</v>
+        <v>51000</v>
       </c>
       <c r="R18">
         <v>0</v>
@@ -1715,83 +1712,14 @@
         </is>
       </c>
       <c r="V18" s="2">
-        <v>46224</v>
+        <v>46247</v>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>Globaris; EconoJournal; Vista Energy / SEC; Oil &amp; Gas Journal; auditoría 2026-08-08</t>
+          <t>YPF / Argentina LNG; La Nación; Infobae; Data Energía</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
-        <is>
-          <t>https://econojournal.com.ar/oilgas/vista-energy-pidio-la-adhesion-al-rigi-para-un-proyecto-de-us-5-800-millones-en-vaca-muerta/; https://www.sec.gov/Archives/edgar/data/1762506/000119312526306139/d151775dex1.htm; https://www.ogj.com/exploration-development/news/55394130/vista-seeks-rigi-approval-for-58-billion-bandurria-norte-development</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Argentina LNG</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Proyecto integrado de producción y exportación de gas natural licuado: desarrollo de gas rico en Vaca Muerta, infraestructura dedicada de transporte, plantas de procesamiento y fraccionamiento y dos unidades flotantes de licuefacción (FLNG) por 12 MTPA en el Golfo San Matías.</t>
-        </is>
-      </c>
-      <c r="D19">
-        <v>41</v>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>YPF S.A. (Argentina); Eni S.p.A. (Italia); XRG (Emiratos Árabes Unidos)</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>YPF</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>Petróleo y Gas</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>Midstream</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>Neuquén; Río Negro</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>Patagonia</t>
-        </is>
-      </c>
-      <c r="M19">
-        <v>51000</v>
-      </c>
-      <c r="R19">
-        <v>0</v>
-      </c>
-      <c r="S19" t="inlineStr">
-        <is>
-          <t>En evaluación</t>
-        </is>
-      </c>
-      <c r="V19" s="2">
-        <v>46247</v>
-      </c>
-      <c r="AA19" t="inlineStr">
-        <is>
-          <t>YPF / Argentina LNG; La Nación; Infobae; Data Energía</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
         <is>
           <t>https://argentina-lng.ypf.com/assets/pdf/ENG-Argentina-LNG-Adhesion-RIGI.pdf; https://www.lanacion.com.ar/economia/un-proyecto-por-us51000-millones-impulsado-por-ypf-solicito-la-adhesion-al-rigi-nid13082026/; https://www.infobae.com/economia/2026/08/13/con-una-inversion-de-usd-50000-millones-ypf-presenta-al-rigi-el-mayor-proyecto-de-su-historia-para-exportar-gas-de-vaca-muerta/; https://dataenergia.ar/gas/argentina-lgn-solicitaron-la-adhesion-formal-al-rigi-para-una-inversion-historica-de-u-s-51-000-millones-202681319370</t>
         </is>

--- a/downloads/base_interactiva_pendientes.xlsx
+++ b/downloads/base_interactiva_pendientes.xlsx
@@ -356,7 +356,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AB18"/>
+  <dimension ref="A1:AB20"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="21" max="21" width="20.7109375" style="2" customWidth="1"/>
@@ -1722,6 +1722,131 @@
       <c r="AB18" t="inlineStr">
         <is>
           <t>https://argentina-lng.ypf.com/assets/pdf/ENG-Argentina-LNG-Adhesion-RIGI.pdf; https://www.lanacion.com.ar/economia/un-proyecto-por-us51000-millones-impulsado-por-ypf-solicito-la-adhesion-al-rigi-nid13082026/; https://www.infobae.com/economia/2026/08/13/con-una-inversion-de-usd-50000-millones-ypf-presenta-al-rigi-el-mayor-proyecto-de-su-historia-para-exportar-gas-de-vaca-muerta/; https://dataenergia.ar/gas/argentina-lgn-solicitaron-la-adhesion-formal-al-rigi-para-una-inversion-historica-de-u-s-51-000-millones-202681319370</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Toyota</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Nueva planta dentro del complejo industrial de Toyota en Zárate para producir un vehículo electrificado —descripto por el ministro de Economía como 100% electrificado—, con aproximadamente 70% de la producción destinada a exportación.</t>
+        </is>
+      </c>
+      <c r="D19">
+        <v>42</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Toyota Argentina S.A. (Argentina)</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Tecnología</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Automotriz</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Buenos Aires</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>Zárate</t>
+        </is>
+      </c>
+      <c r="M19">
+        <v>1341</v>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>En evaluación</t>
+        </is>
+      </c>
+      <c r="T19">
+        <v>6200</v>
+      </c>
+      <c r="V19" s="2">
+        <v>46295</v>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>Luis Caputo / Ministerio de Economía (X, 30/09/2026); Reuters (30/09/2026); La Nación / Toyota Argentina (30/09/2026); ARCA / Decreto 105/2026 (19/02/2026)</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>https://x.com/LuisCaputoAR/status/2105382049758523681; https://www.reuters.com/world/asia-pacific/toyota-invest-134-billion-argentina-production-plant-2026-09-30/; https://www.lanacion.com.ar/autos/toyota-invertira-us1341-millones-para-fabricar-un-nuevo-vehiculo-en-la-argentina-nid30092026/; https://biblioteca.afip.gob.ar/dcp/DEC_C_000749_2024_08_22</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>PAE Cerro Dragón</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Desarrollo de recuperación terciaria de petróleo convencional en Cerro Dragón: 22 plantas de inyección de polímeros, perforación de 100 pozos productores e inyectores, adecuación de pozos, intervención de otros 600 pozos productores e infraestructura complementaria de superficie. Producción incremental estimada: 46 millones de barriles de petróleo y 30 BCF de gas natural.</t>
+        </is>
+      </c>
+      <c r="D20">
+        <v>43</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Pan American Energy (PAE) (Argentina)</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Petróleo y Gas</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>Upstream</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Chubut</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>Área Cerro Dragón, Cuenca del Golfo San Jorge</t>
+        </is>
+      </c>
+      <c r="M20">
+        <v>1200</v>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>En evaluación</t>
+        </is>
+      </c>
+      <c r="V20" s="2">
+        <v>46296</v>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>Gobierno del Chubut (01/10/2026); La Nación / PAE (01/10/2026); Reuters / Luis Caputo (01/10/2026)</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>https://noticias.chubut.gob.ar/notas/gobierno/5481/torres-encabezo-en-la-sede-de-la-ocde-el-anuncio-de-una-inversion-de-usd-1200-millones-de-pae-para-cerro-dragon.html; https://www.lanacion.com.ar/economia/pan-american-energy-busca-ingresar-al-rigi-con-una-inversion-de-us1200-millones-para-revitalizar-nid01102026/; https://www.reuters.com/business/energy/pae-invest-12-billion-argentina-oil-field-minister-says-2026-10-01/</t>
         </is>
       </c>
     </row>

--- a/downloads/base_interactiva_pendientes.xlsx
+++ b/downloads/base_interactiva_pendientes.xlsx
@@ -356,7 +356,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AB20"/>
+  <dimension ref="A1:AB21"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="21" max="21" width="20.7109375" style="2" customWidth="1"/>
@@ -1847,6 +1847,75 @@
       <c r="AB20" t="inlineStr">
         <is>
           <t>https://noticias.chubut.gob.ar/notas/gobierno/5481/torres-encabezo-en-la-sede-de-la-ocde-el-anuncio-de-una-inversion-de-usd-1200-millones-de-pae-para-cerro-dragon.html; https://www.lanacion.com.ar/economia/pan-american-energy-busca-ingresar-al-rigi-con-una-inversion-de-us1200-millones-para-revitalizar-nid01102026/; https://www.reuters.com/business/energy/pae-invest-12-billion-argentina-oil-field-minister-says-2026-10-01/</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Pampa Exploración S.A.</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Desarrollo del depósito Lunahuasi de cobre, oro y plata, actualmente en exploración, con perforaciones y una galería de exploración planificada para avanzar hacia su desarrollo minero</t>
+        </is>
+      </c>
+      <c r="D21">
+        <v>44</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>NGEx Minerals Ltd. (Canadá)</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Pampa Exploración S.A.</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Minería</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Cobre</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>San Juan</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>Departamento Iglesia; Distrito Vicuña</t>
+        </is>
+      </c>
+      <c r="M21">
+        <v>2437</v>
+      </c>
+      <c r="R21">
+        <v>0</v>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>En evaluación</t>
+        </is>
+      </c>
+      <c r="V21" s="2">
+        <v>46113</v>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>NGEx Minerals, 14/05/2026; Panorama Minero, consulta 02/10/2026</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>https://ngexminerals.com/news/ngex-releases-2025-sustainability-summary-122811/; https://www.panorama-minero.com/es/mining-compendium/argentina/project/lunahuasi</t>
         </is>
       </c>
     </row>

--- a/downloads/base_interactiva_pendientes.xlsx
+++ b/downloads/base_interactiva_pendientes.xlsx
@@ -696,10 +696,10 @@
         </is>
       </c>
       <c r="M4">
-        <v>12000</v>
+        <v>12400</v>
       </c>
       <c r="N4">
-        <v>12000</v>
+        <v>12400</v>
       </c>
       <c r="R4">
         <v>0</v>
@@ -709,17 +709,20 @@
           <t>En evaluación</t>
         </is>
       </c>
+      <c r="T4">
+        <v>6990</v>
+      </c>
       <c r="V4" s="2">
         <v>45771</v>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>Globaris; Gobierno de Neuquén; EconoJournal; Luis Caputo; Clarín; auditoría 2026-08-08</t>
+          <t>Globaris; Gobierno de Neuquén; EconoJournal; Luis Caputo; Clarín; La Nación; Bloomberg</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>https://www.neuqueninforma.gob.ar/noticias/2026/04/23/256641-neuquen-suma-un-nuevo-megaproyecto-al-rigi-con-apoyo-de-gyp; https://econojournal.com.ar/oilgas/pluspetrol-solicito-la-adhesion-al-rigi-para-el-bloque-bajo-del-choique-la-invernada-con-una-inversion-de-us12-000-millones/; https://x.com/LuisCaputoAR/status/2047621135127269495; https://www.clarin.com/economia/rigi-vaca-muerta-pluspetrol-presento-inversiones-us-12000-millones-campo-compro-exxon_0_gYALiNgXD0.html</t>
+          <t>https://www.neuqueninforma.gob.ar/noticias/2026/04/23/256641-neuquen-suma-un-nuevo-megaproyecto-al-rigi-con-apoyo-de-gyp; https://econojournal.com.ar/oilgas/pluspetrol-solicito-la-adhesion-al-rigi-para-el-bloque-bajo-del-choique-la-invernada-con-una-inversion-de-us12-000-millones/; https://x.com/LuisCaputoAR/status/2047621135127269495; https://www.clarin.com/economia/rigi-vaca-muerta-pluspetrol-presento-inversiones-us-12000-millones-campo-compro-exxon_0_gYALiNgXD0.html; https://www.lanacion.com.ar/economia/pluspetrol-y-gyp-obtuvieron-el-rigi-para-un-proyecto-de-us12400-millones-en-vaca-muerta-nid02102026/; https://www.bloomberglinea.com/latinoamerica/argentina/pluspetrol-recibe-luz-verde-del-rigi-para-invertir-us12400-millones-en-vaca-muerta/</t>
         </is>
       </c>
     </row>
@@ -1904,9 +1907,6 @@
         <is>
           <t>En evaluación</t>
         </is>
-      </c>
-      <c r="V21" s="2">
-        <v>46113</v>
       </c>
       <c r="AA21" t="inlineStr">
         <is>

--- a/downloads/base_interactiva_pendientes.xlsx
+++ b/downloads/base_interactiva_pendientes.xlsx
@@ -356,7 +356,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AB21"/>
+  <dimension ref="A1:AB20"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="21" max="21" width="20.7109375" style="2" customWidth="1"/>
@@ -1086,52 +1086,52 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Planta de Tratamiento Los Toldos</t>
+          <t>Pozuelos Pastos Grandes (PPG)</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Desarrollo del área no convencional Los Toldos II Este, en Neuquén, con una planta central de procesamiento de crudo, perforación de pozos y sistemas de recolección y evacuación. El proyecto apunta a alcanzar una producción cercana a 70.000 barriles diarios.</t>
+          <t>Desarrollo integrado de litio en los salares Pozuelos y Pastos Grandes, en la Puna salteña, mediante una operación conjunta de Ganfeng Lithium y Lithium Argentina. El plan contempla infraestructura de extracción y procesamiento y una expansión por etapas hasta una capacidad objetivo de 150.000 toneladas anuales de carbonato de litio equivalente.</t>
         </is>
       </c>
       <c r="D10">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Tecpetrol S.A. (Argentina); Gas y Petróleo del Neuquén S.A. (Argentina)</t>
+          <t>Ganfeng Lithium (China); Lithium Argentina AG (Suiza)</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tecpetrol S.A – Gas y Petróleo del Neuquén S.A. (UT)</t>
+          <t>Lithea Inc.</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Petróleo y Gas</t>
+          <t>Minería</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Upstream</t>
+          <t>Litio</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>Neuquén</t>
+          <t>Salta</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>Patagonia</t>
+          <t>NOA</t>
         </is>
       </c>
       <c r="M10">
-        <v>6391</v>
+        <v>4245</v>
       </c>
       <c r="N10">
-        <v>6391</v>
+        <v>4245</v>
       </c>
       <c r="R10">
         <v>0</v>
@@ -1142,41 +1142,41 @@
         </is>
       </c>
       <c r="V10" s="2">
-        <v>46118</v>
+        <v>46081</v>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>Globaris; Techint Ingeniería y Construcción; Vaca Muerta News; Infobae; auditoría 2026-08-08</t>
+          <t>Globaris; Gobierno de Salta; Lithium Argentina; Infobae; auditoría 2026-08-08</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>https://www.techint.com/es/nuestros-proyectos/los-toldos-ii-este; https://vacamuertanews.com/amp/a-30-km-de-rincon-de-los-sauces-tecpetrol-y-gyp-lanzan-un-megaproyecto-de-shale-oil-con-380-pozos.htm; https://www.infobae.com/economia/2026/05/13/el-gobierno-aprobo-el-ingreso-al-rigi-de-la-ampliacion-del-gasoducto-perito-moreno-con-una-inversion-de-usd-550-millones/</t>
+          <t>https://www.salta.gob.ar/prensa/noticias/avanza-en-salta-el-proyecto-de-litio-pozuelos-pastos-grandes-104827; https://investors.lithium-argentina.com/news-releases/news-release-details/lithium-argentina-reports-fourth-quarter-and-full-year-2025; https://www.infobae.com/economia/2026/05/13/el-gobierno-aprobo-el-ingreso-al-rigi-de-la-ampliacion-del-gasoducto-perito-moreno-con-una-inversion-de-usd-550-millones/</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Pozuelos Pastos Grandes (PPG)</t>
+          <t>Sal de Vida</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Desarrollo integrado de litio en los salares Pozuelos y Pastos Grandes, en la Puna salteña, mediante una operación conjunta de Ganfeng Lithium y Lithium Argentina. El plan contempla infraestructura de extracción y procesamiento y una expansión por etapas hasta una capacidad objetivo de 150.000 toneladas anuales de carbonato de litio equivalente.</t>
+          <t>Desarrollo de litio en el Salar del Hombre Muerto, Catamarca, con extracción de salmuera e instalaciones de procesamiento. La primera etapa prevé una capacidad de aproximadamente 15.000 toneladas anuales de carbonato de litio equivalente.</t>
         </is>
       </c>
       <c r="D11">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Ganfeng Lithium (China); Lithium Argentina AG (Suiza)</t>
+          <t>Rio Tinto (Reino Unido)</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lithea Inc.</t>
+          <t>Sal de Vida S.A.</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1191,7 +1191,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>Salta</t>
+          <t>Catamarca</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1200,10 +1200,10 @@
         </is>
       </c>
       <c r="M11">
-        <v>4245</v>
+        <v>818</v>
       </c>
       <c r="N11">
-        <v>4245</v>
+        <v>818</v>
       </c>
       <c r="R11">
         <v>0</v>
@@ -1214,68 +1214,68 @@
         </is>
       </c>
       <c r="V11" s="2">
-        <v>46081</v>
+        <v>45758</v>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>Globaris; Gobierno de Salta; Lithium Argentina; Infobae; auditoría 2026-08-08</t>
+          <t>Globaris; Rio Tinto; Infobae; auditoría 2026-08-08</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>https://www.salta.gob.ar/prensa/noticias/avanza-en-salta-el-proyecto-de-litio-pozuelos-pastos-grandes-104827; https://investors.lithium-argentina.com/news-releases/news-release-details/lithium-argentina-reports-fourth-quarter-and-full-year-2025; https://www.infobae.com/economia/2026/05/13/el-gobierno-aprobo-el-ingreso-al-rigi-de-la-ampliacion-del-gasoducto-perito-moreno-con-una-inversion-de-usd-550-millones/</t>
+          <t>https://www.riotinto.com/en/news/releases/2025/rio-tinto-confirmed-as-preferred-partner-on-world-class-salares-altoandinos-lithium-project; https://www.infobae.com/economia/2025/10/07/hay-mas-de-usd-18000-millones-a-la-espera-de-aprobacion-en-proyectos-del-rigi/; https://www.infobae.com/economia/2026/05/13/el-gobierno-aprobo-el-ingreso-al-rigi-de-la-ampliacion-del-gasoducto-perito-moreno-con-una-inversion-de-usd-550-millones/</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Sal de Vida</t>
+          <t>Loma Jarillosa Este y Puesto Silva Oeste</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Desarrollo de litio en el Salar del Hombre Muerto, Catamarca, con extracción de salmuera e instalaciones de procesamiento. La primera etapa prevé una capacidad de aproximadamente 15.000 toneladas anuales de carbonato de litio equivalente.</t>
+          <t>Desarrollo integrado de petróleo no convencional en los bloques Loma Jarillosa Este y Puesto Silva Oeste, en Vaca Muerta, mediante perforación en modo factoría, una planta central de procesamiento y sistemas compartidos de evacuación. El plan busca elevar la producción conjunta hasta unos 20.000 barriles equivalentes diarios en tres años.</t>
         </is>
       </c>
       <c r="D12">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Rio Tinto (Reino Unido)</t>
+          <t>GeoPark (Colombia); Gas y Petróleo del Neuquén S.A. (Argentina)</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Sal de Vida S.A.</t>
+          <t>GeoPark</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Minería</t>
+          <t>Petróleo y Gas</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Litio</t>
+          <t>Upstream</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>Catamarca</t>
+          <t>Neuquén</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>NOA</t>
+          <t>Patagonia</t>
         </is>
       </c>
       <c r="M12">
-        <v>818</v>
+        <v>1000</v>
       </c>
       <c r="N12">
-        <v>818</v>
+        <v>1000</v>
       </c>
       <c r="R12">
         <v>0</v>
@@ -1286,68 +1286,68 @@
         </is>
       </c>
       <c r="V12" s="2">
-        <v>45758</v>
+        <v>46157</v>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>Globaris; Rio Tinto; Infobae; auditoría 2026-08-08</t>
+          <t>Globaris; GeoPark; EconoJournal; auditoría 2026-08-08</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>https://www.riotinto.com/en/news/releases/2025/rio-tinto-confirmed-as-preferred-partner-on-world-class-salares-altoandinos-lithium-project; https://www.infobae.com/economia/2025/10/07/hay-mas-de-usd-18000-millones-a-la-espera-de-aprobacion-en-proyectos-del-rigi/; https://www.infobae.com/economia/2026/05/13/el-gobierno-aprobo-el-ingreso-al-rigi-de-la-ampliacion-del-gasoducto-perito-moreno-con-una-inversion-de-usd-550-millones/</t>
+          <t>https://www.geo-park.com/es/news/geopark-solicita-adhesion-al-rigi-por-proyecto-de-inversion/; https://econojournal.com.ar/oilgas/geopark-presenta-al-rigi-una-inversion-por-us1-000-millones-para-un-hub-petrolero-en-vaca-muerta/</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Loma Jarillosa Este y Puesto Silva Oeste</t>
+          <t>Minera Agua Rica (MARA)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Desarrollo integrado de petróleo no convencional en los bloques Loma Jarillosa Este y Puesto Silva Oeste, en Vaca Muerta, mediante perforación en modo factoría, una planta central de procesamiento y sistemas compartidos de evacuación. El plan busca elevar la producción conjunta hasta unos 20.000 barriles equivalentes diarios en tres años.</t>
+          <t>Desarrollo de una mina de cobre, oro, plata y molibdeno en Catamarca, integrando el yacimiento Agua Rica con la infraestructura existente de Alumbrera, ubicada a unos 35 km. El esquema MARA contempla explotación, procesamiento y uso de instalaciones compartidas para producción destinada principalmente a exportación.</t>
         </is>
       </c>
       <c r="D13">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>GeoPark (Colombia); Gas y Petróleo del Neuquén S.A. (Argentina)</t>
+          <t>Glencore (Suiza)</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>GeoPark</t>
+          <t>Minera Agua Rica LLC Sucursal Argentina</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Petróleo y Gas</t>
+          <t>Minería</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Upstream</t>
+          <t>Cobre</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>Neuquén</t>
+          <t>Catamarca</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>Patagonia</t>
+          <t>NOA</t>
         </is>
       </c>
       <c r="M13">
-        <v>1000</v>
+        <v>4000</v>
       </c>
       <c r="N13">
-        <v>1000</v>
+        <v>4000</v>
       </c>
       <c r="R13">
         <v>0</v>
@@ -1358,41 +1358,41 @@
         </is>
       </c>
       <c r="V13" s="2">
-        <v>46157</v>
+        <v>45887</v>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>Globaris; GeoPark; EconoJournal; auditoría 2026-08-08</t>
+          <t>Globaris; Glencore; Luis Caputo; Reuters; Infobae; auditoría 2026-08-08</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>https://www.geo-park.com/es/news/geopark-solicita-adhesion-al-rigi-por-proyecto-de-inversion/; https://econojournal.com.ar/oilgas/geopark-presenta-al-rigi-una-inversion-por-us1-000-millones-para-un-hub-petrolero-en-vaca-muerta/</t>
+          <t>https://www.glencore.com/media-and-insights/news/glencore-submits-RIGI-applications-in-respect-of-its-argentine-copper-projects; https://x.com/LuisCaputoAR/status/1957458679835594969; https://www.reuters.com/latam/negocio/7X5ZW2SXG5IYNBUILMTT6GMS6U-2025-08-21/; https://www.infobae.com/economia/2026/05/13/el-gobierno-aprobo-el-ingreso-al-rigi-de-la-ampliacion-del-gasoducto-perito-moreno-con-una-inversion-de-usd-550-millones/</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Minera Agua Rica (MARA)</t>
+          <t>Jama Solaroz</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Desarrollo de una mina de cobre, oro, plata y molibdeno en Catamarca, integrando el yacimiento Agua Rica con la infraestructura existente de Alumbrera, ubicada a unos 35 km. El esquema MARA contempla explotación, procesamiento y uso de instalaciones compartidas para producción destinada principalmente a exportación.</t>
+          <t>Desarrollo integrado de litio en los proyectos Jama y Solaroz, en la Puna de Jujuy, con una planta prevista en el Salar de Jama. La iniciativa contempla extracción de salmuera y producción de compuestos de litio, con una capacidad informada de aproximadamente 22.000 toneladas anuales.</t>
         </is>
       </c>
       <c r="D14">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Glencore (Suiza)</t>
+          <t>CNGR Advanced Material Co., Ltd. (China)</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Minera Agua Rica LLC Sucursal Argentina</t>
+          <t>CNGR Advanced Material Co., Ltd.</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1402,12 +1402,12 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Cobre</t>
+          <t>Litio</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>Catamarca</t>
+          <t>Jujuy</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -1416,10 +1416,10 @@
         </is>
       </c>
       <c r="M14">
-        <v>4000</v>
+        <v>1151</v>
       </c>
       <c r="N14">
-        <v>4000</v>
+        <v>1151</v>
       </c>
       <c r="R14">
         <v>0</v>
@@ -1430,68 +1430,68 @@
         </is>
       </c>
       <c r="V14" s="2">
-        <v>45887</v>
+        <v>46111</v>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>Globaris; Glencore; Luis Caputo; Reuters; Infobae; auditoría 2026-08-08</t>
+          <t>Globaris; Gobierno de Jujuy; El Tribuno de Jujuy; Infobae; auditoría 2026-08-08</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>https://www.glencore.com/media-and-insights/news/glencore-submits-RIGI-applications-in-respect-of-its-argentine-copper-projects; https://x.com/LuisCaputoAR/status/1957458679835594969; https://www.reuters.com/latam/negocio/7X5ZW2SXG5IYNBUILMTT6GMS6U-2025-08-21/; https://www.infobae.com/economia/2026/05/13/el-gobierno-aprobo-el-ingreso-al-rigi-de-la-ampliacion-del-gasoducto-perito-moreno-con-una-inversion-de-usd-550-millones/</t>
+          <t>https://prensa.jujuy.gob.ar/jujuy/jujuy-se-afianza-como-productor-minerales-criticos-el-desarrollo-la-transicion-energetica-n120116; https://eltribunodejujuy.com/informacion-general/2026-4-1-0-0-0-proyecto-de-litio-en-jujuy-busca-la-adhesion-al-rigi; https://www.infobae.com/economia/2026/05/13/el-gobierno-aprobo-el-ingreso-al-rigi-de-la-ampliacion-del-gasoducto-perito-moreno-con-una-inversion-de-usd-550-millones/</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Jama Solaroz</t>
+          <t>LLL Oil</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Desarrollo integrado de litio en los proyectos Jama y Solaroz, en la Puna de Jujuy, con una planta prevista en el Salar de Jama. La iniciativa contempla extracción de salmuera y producción de compuestos de litio, con una capacidad informada de aproximadamente 22.000 toneladas anuales.</t>
+          <t>Desarrollo integrado de cinco bloques contiguos de petróleo no convencional en Vaca Muerta: La Angostura Norte, La Angostura Sur I, La Angostura Sur II, La Angostura Suroeste y Barreal Grande. El programa prevé perforar 1.152 pozos y compartir instalaciones de superficie y servicios para alcanzar una producción aproximada de 240.000 barriles diarios hacia 2032, destinada a exportación.</t>
         </is>
       </c>
       <c r="D15">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>CNGR Advanced Material Co., Ltd. (China)</t>
+          <t>YPF S.A. (Argentina)</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>CNGR Advanced Material Co., Ltd.</t>
+          <t>YPF</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Minería</t>
+          <t>Petróleo y Gas</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Litio</t>
+          <t>Upstream</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>Jujuy</t>
+          <t>Neuquén</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>NOA</t>
+          <t>Patagonia</t>
         </is>
       </c>
       <c r="M15">
-        <v>1151</v>
+        <v>25000</v>
       </c>
       <c r="N15">
-        <v>1151</v>
+        <v>25000</v>
       </c>
       <c r="R15">
         <v>0</v>
@@ -1502,41 +1502,41 @@
         </is>
       </c>
       <c r="V15" s="2">
-        <v>46111</v>
+        <v>46157</v>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>Globaris; Gobierno de Jujuy; El Tribuno de Jujuy; Infobae; auditoría 2026-08-08</t>
+          <t>Globaris; YPF; EconoJournal; Reuters; auditoría 2026-08-08</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>https://prensa.jujuy.gob.ar/jujuy/jujuy-se-afianza-como-productor-minerales-criticos-el-desarrollo-la-transicion-energetica-n120116; https://eltribunodejujuy.com/informacion-general/2026-4-1-0-0-0-proyecto-de-litio-en-jujuy-busca-la-adhesion-al-rigi; https://www.infobae.com/economia/2026/05/13/el-gobierno-aprobo-el-ingreso-al-rigi-de-la-ampliacion-del-gasoducto-perito-moreno-con-una-inversion-de-usd-550-millones/</t>
+          <t>https://www.instagram.com/p/DYX1JXjj-bC/; https://econojournal.com.ar/destacada/ypf-presento-rigi-acelerar-produccion-petroleo-vaca-muerta/; https://www.reuters.com/business/energy/argentinas-ypf-registers-25-bln-oil-project-rigi-investment-scheme-2026-05-15/</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>LLL Oil</t>
+          <t>Bandurria Norte</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Desarrollo integrado de cinco bloques contiguos de petróleo no convencional en Vaca Muerta: La Angostura Norte, La Angostura Sur I, La Angostura Sur II, La Angostura Suroeste y Barreal Grande. El programa prevé perforar 1.152 pozos y compartir instalaciones de superficie y servicios para alcanzar una producción aproximada de 240.000 barriles diarios hacia 2032, destinada a exportación.</t>
+          <t>Desarrollo greenfield de petróleo no convencional en Bandurria Norte, Vaca Muerta, sobre una superficie aproximada de 26.500 acres. El plan contempla 332 pozos horizontales, planta de tratamiento de crudo, compresión de gas, redes de recolección y ductos, con una meta de 50.000 barriles equivalentes diarios.</t>
         </is>
       </c>
       <c r="D16">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>YPF S.A. (Argentina)</t>
+          <t>Vista Energy (Argentina)</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>YPF</t>
+          <t>Vista Energy</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1560,10 +1560,10 @@
         </is>
       </c>
       <c r="M16">
-        <v>25000</v>
+        <v>5800</v>
       </c>
       <c r="N16">
-        <v>25000</v>
+        <v>5800</v>
       </c>
       <c r="R16">
         <v>0</v>
@@ -1574,41 +1574,41 @@
         </is>
       </c>
       <c r="V16" s="2">
-        <v>46157</v>
+        <v>46224</v>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>Globaris; YPF; EconoJournal; Reuters; auditoría 2026-08-08</t>
+          <t>Globaris; EconoJournal; Vista Energy / SEC; Oil &amp; Gas Journal; auditoría 2026-08-08</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DYX1JXjj-bC/; https://econojournal.com.ar/destacada/ypf-presento-rigi-acelerar-produccion-petroleo-vaca-muerta/; https://www.reuters.com/business/energy/argentinas-ypf-registers-25-bln-oil-project-rigi-investment-scheme-2026-05-15/</t>
+          <t>https://econojournal.com.ar/oilgas/vista-energy-pidio-la-adhesion-al-rigi-para-un-proyecto-de-us-5-800-millones-en-vaca-muerta/; https://www.sec.gov/Archives/edgar/data/1762506/000119312526306139/d151775dex1.htm; https://www.ogj.com/exploration-development/news/55394130/vista-seeks-rigi-approval-for-58-billion-bandurria-norte-development</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Bandurria Norte</t>
+          <t>Argentina LNG</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Desarrollo greenfield de petróleo no convencional en Bandurria Norte, Vaca Muerta, sobre una superficie aproximada de 26.500 acres. El plan contempla 332 pozos horizontales, planta de tratamiento de crudo, compresión de gas, redes de recolección y ductos, con una meta de 50.000 barriles equivalentes diarios.</t>
+          <t>Proyecto integrado de producción y exportación de gas natural licuado: desarrollo de gas rico en Vaca Muerta, infraestructura dedicada de transporte, plantas de procesamiento y fraccionamiento y dos unidades flotantes de licuefacción (FLNG) por 12 MTPA en el Golfo San Matías.</t>
         </is>
       </c>
       <c r="D17">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Vista Energy (Argentina)</t>
+          <t>YPF S.A. (Argentina); Eni S.p.A. (Italia); XRG (Emiratos Árabes Unidos)</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vista Energy</t>
+          <t>YPF</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1618,12 +1618,12 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Upstream</t>
+          <t>Midstream</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>Neuquén</t>
+          <t>Neuquén; Río Negro</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -1632,10 +1632,7 @@
         </is>
       </c>
       <c r="M17">
-        <v>5800</v>
-      </c>
-      <c r="N17">
-        <v>5800</v>
+        <v>51000</v>
       </c>
       <c r="R17">
         <v>0</v>
@@ -1646,274 +1643,205 @@
         </is>
       </c>
       <c r="V17" s="2">
-        <v>46224</v>
+        <v>46247</v>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>Globaris; EconoJournal; Vista Energy / SEC; Oil &amp; Gas Journal; auditoría 2026-08-08</t>
+          <t>YPF / Argentina LNG; La Nación; Infobae; Data Energía</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>https://econojournal.com.ar/oilgas/vista-energy-pidio-la-adhesion-al-rigi-para-un-proyecto-de-us-5-800-millones-en-vaca-muerta/; https://www.sec.gov/Archives/edgar/data/1762506/000119312526306139/d151775dex1.htm; https://www.ogj.com/exploration-development/news/55394130/vista-seeks-rigi-approval-for-58-billion-bandurria-norte-development</t>
+          <t>https://argentina-lng.ypf.com/assets/pdf/ENG-Argentina-LNG-Adhesion-RIGI.pdf; https://www.lanacion.com.ar/economia/un-proyecto-por-us51000-millones-impulsado-por-ypf-solicito-la-adhesion-al-rigi-nid13082026/; https://www.infobae.com/economia/2026/08/13/con-una-inversion-de-usd-50000-millones-ypf-presenta-al-rigi-el-mayor-proyecto-de-su-historia-para-exportar-gas-de-vaca-muerta/; https://dataenergia.ar/gas/argentina-lgn-solicitaron-la-adhesion-formal-al-rigi-para-una-inversion-historica-de-u-s-51-000-millones-202681319370</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Argentina LNG</t>
+          <t>Toyota</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Proyecto integrado de producción y exportación de gas natural licuado: desarrollo de gas rico en Vaca Muerta, infraestructura dedicada de transporte, plantas de procesamiento y fraccionamiento y dos unidades flotantes de licuefacción (FLNG) por 12 MTPA en el Golfo San Matías.</t>
+          <t>Nueva planta dentro del complejo industrial de Toyota en Zárate para producir un vehículo electrificado —descripto por el ministro de Economía como 100% electrificado—, con aproximadamente 70% de la producción destinada a exportación.</t>
         </is>
       </c>
       <c r="D18">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>YPF S.A. (Argentina); Eni S.p.A. (Italia); XRG (Emiratos Árabes Unidos)</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>YPF</t>
+          <t>Toyota Argentina S.A. (Argentina)</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Petróleo y Gas</t>
+          <t>Tecnología</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Midstream</t>
+          <t>Automotriz</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>Neuquén; Río Negro</t>
+          <t>Buenos Aires</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>Patagonia</t>
+          <t>Zárate</t>
         </is>
       </c>
       <c r="M18">
-        <v>51000</v>
-      </c>
-      <c r="R18">
-        <v>0</v>
+        <v>1341</v>
       </c>
       <c r="S18" t="inlineStr">
         <is>
           <t>En evaluación</t>
         </is>
       </c>
+      <c r="T18">
+        <v>6200</v>
+      </c>
       <c r="V18" s="2">
-        <v>46247</v>
+        <v>46295</v>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>YPF / Argentina LNG; La Nación; Infobae; Data Energía</t>
+          <t>Luis Caputo / Ministerio de Economía (X, 30/09/2026); Reuters (30/09/2026); La Nación / Toyota Argentina (30/09/2026); ARCA / Decreto 105/2026 (19/02/2026)</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>https://argentina-lng.ypf.com/assets/pdf/ENG-Argentina-LNG-Adhesion-RIGI.pdf; https://www.lanacion.com.ar/economia/un-proyecto-por-us51000-millones-impulsado-por-ypf-solicito-la-adhesion-al-rigi-nid13082026/; https://www.infobae.com/economia/2026/08/13/con-una-inversion-de-usd-50000-millones-ypf-presenta-al-rigi-el-mayor-proyecto-de-su-historia-para-exportar-gas-de-vaca-muerta/; https://dataenergia.ar/gas/argentina-lgn-solicitaron-la-adhesion-formal-al-rigi-para-una-inversion-historica-de-u-s-51-000-millones-202681319370</t>
+          <t>https://x.com/LuisCaputoAR/status/2105382049758523681; https://www.reuters.com/world/asia-pacific/toyota-invest-134-billion-argentina-production-plant-2026-09-30/; https://www.lanacion.com.ar/autos/toyota-invertira-us1341-millones-para-fabricar-un-nuevo-vehiculo-en-la-argentina-nid30092026/; https://biblioteca.afip.gob.ar/dcp/DEC_C_000749_2024_08_22</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Toyota</t>
+          <t>PAE Cerro Dragón</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Nueva planta dentro del complejo industrial de Toyota en Zárate para producir un vehículo electrificado —descripto por el ministro de Economía como 100% electrificado—, con aproximadamente 70% de la producción destinada a exportación.</t>
+          <t>Desarrollo de recuperación terciaria de petróleo convencional en Cerro Dragón: 22 plantas de inyección de polímeros, perforación de 100 pozos productores e inyectores, adecuación de pozos, intervención de otros 600 pozos productores e infraestructura complementaria de superficie. Producción incremental estimada: 46 millones de barriles de petróleo y 30 BCF de gas natural.</t>
         </is>
       </c>
       <c r="D19">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Toyota Argentina S.A. (Argentina)</t>
+          <t>Pan American Energy (PAE) (Argentina)</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Tecnología</t>
+          <t>Petróleo y Gas</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Automotriz</t>
+          <t>Upstream</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>Buenos Aires</t>
+          <t>Chubut</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>Zárate</t>
+          <t>Área Cerro Dragón, Cuenca del Golfo San Jorge</t>
         </is>
       </c>
       <c r="M19">
-        <v>1341</v>
+        <v>1200</v>
       </c>
       <c r="S19" t="inlineStr">
         <is>
           <t>En evaluación</t>
         </is>
       </c>
-      <c r="T19">
-        <v>6200</v>
-      </c>
       <c r="V19" s="2">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>Luis Caputo / Ministerio de Economía (X, 30/09/2026); Reuters (30/09/2026); La Nación / Toyota Argentina (30/09/2026); ARCA / Decreto 105/2026 (19/02/2026)</t>
+          <t>Gobierno del Chubut (01/10/2026); La Nación / PAE (01/10/2026); Reuters / Luis Caputo (01/10/2026)</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>https://x.com/LuisCaputoAR/status/2105382049758523681; https://www.reuters.com/world/asia-pacific/toyota-invest-134-billion-argentina-production-plant-2026-09-30/; https://www.lanacion.com.ar/autos/toyota-invertira-us1341-millones-para-fabricar-un-nuevo-vehiculo-en-la-argentina-nid30092026/; https://biblioteca.afip.gob.ar/dcp/DEC_C_000749_2024_08_22</t>
+          <t>https://noticias.chubut.gob.ar/notas/gobierno/5481/torres-encabezo-en-la-sede-de-la-ocde-el-anuncio-de-una-inversion-de-usd-1200-millones-de-pae-para-cerro-dragon.html; https://www.lanacion.com.ar/economia/pan-american-energy-busca-ingresar-al-rigi-con-una-inversion-de-us1200-millones-para-revitalizar-nid01102026/; https://www.reuters.com/business/energy/pae-invest-12-billion-argentina-oil-field-minister-says-2026-10-01/</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>PAE Cerro Dragón</t>
+          <t>Pampa Exploración S.A.</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Desarrollo de recuperación terciaria de petróleo convencional en Cerro Dragón: 22 plantas de inyección de polímeros, perforación de 100 pozos productores e inyectores, adecuación de pozos, intervención de otros 600 pozos productores e infraestructura complementaria de superficie. Producción incremental estimada: 46 millones de barriles de petróleo y 30 BCF de gas natural.</t>
+          <t>Desarrollo del depósito Lunahuasi de cobre, oro y plata, actualmente en exploración, con perforaciones y una galería de exploración planificada para avanzar hacia su desarrollo minero</t>
         </is>
       </c>
       <c r="D20">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Pan American Energy (PAE) (Argentina)</t>
+          <t>NGEx Minerals Ltd. (Canadá)</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Pampa Exploración S.A.</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Petróleo y Gas</t>
+          <t>Minería</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Upstream</t>
+          <t>Cobre</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>Chubut</t>
+          <t>San Juan</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>Área Cerro Dragón, Cuenca del Golfo San Jorge</t>
+          <t>Departamento Iglesia; Distrito Vicuña</t>
         </is>
       </c>
       <c r="M20">
-        <v>1200</v>
+        <v>2437</v>
+      </c>
+      <c r="R20">
+        <v>0</v>
       </c>
       <c r="S20" t="inlineStr">
         <is>
           <t>En evaluación</t>
         </is>
       </c>
-      <c r="V20" s="2">
-        <v>46296</v>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>Gobierno del Chubut (01/10/2026); La Nación / PAE (01/10/2026); Reuters / Luis Caputo (01/10/2026)</t>
+          <t>NGEx Minerals, 14/05/2026; Panorama Minero, consulta 02/10/2026</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
-        <is>
-          <t>https://noticias.chubut.gob.ar/notas/gobierno/5481/torres-encabezo-en-la-sede-de-la-ocde-el-anuncio-de-una-inversion-de-usd-1200-millones-de-pae-para-cerro-dragon.html; https://www.lanacion.com.ar/economia/pan-american-energy-busca-ingresar-al-rigi-con-una-inversion-de-us1200-millones-para-revitalizar-nid01102026/; https://www.reuters.com/business/energy/pae-invest-12-billion-argentina-oil-field-minister-says-2026-10-01/</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Pampa Exploración S.A.</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Desarrollo del depósito Lunahuasi de cobre, oro y plata, actualmente en exploración, con perforaciones y una galería de exploración planificada para avanzar hacia su desarrollo minero</t>
-        </is>
-      </c>
-      <c r="D21">
-        <v>44</v>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>NGEx Minerals Ltd. (Canadá)</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>Pampa Exploración S.A.</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>Minería</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>Cobre</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>San Juan</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>Departamento Iglesia; Distrito Vicuña</t>
-        </is>
-      </c>
-      <c r="M21">
-        <v>2437</v>
-      </c>
-      <c r="R21">
-        <v>0</v>
-      </c>
-      <c r="S21" t="inlineStr">
-        <is>
-          <t>En evaluación</t>
-        </is>
-      </c>
-      <c r="AA21" t="inlineStr">
-        <is>
-          <t>NGEx Minerals, 14/05/2026; Panorama Minero, consulta 02/10/2026</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
         <is>
           <t>https://ngexminerals.com/news/ngex-releases-2025-sustainability-summary-122811/; https://www.panorama-minero.com/es/mining-compendium/argentina/project/lunahuasi</t>
         </is>

--- a/downloads/base_interactiva_pendientes.xlsx
+++ b/downloads/base_interactiva_pendientes.xlsx
@@ -356,7 +356,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AB20"/>
+  <dimension ref="A1:AB19"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="21" max="21" width="20.7109375" style="2" customWidth="1"/>
@@ -654,25 +654,25 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Bajo del Choique–La Invernada</t>
+          <t>Duplicar Norte</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Desarrollo no convencional de petróleo y gas en los bloques Bajo del Choique–La Invernada, en Vaca Muerta. Contempla la perforación de más de 600 pozos, plantas de procesamiento, ductos e infraestructura asociada, con objetivos de hasta 100.000 barriles diarios de petróleo y 12 millones de m³ diarios de gas.</t>
+          <t>Construcción de un oleoducto de aproximadamente 207 km entre el área de Auca Mahuida/Puesto Hernández, en Neuquén, y Allen, en Río Negro, junto con obras de repotenciación y medición. La ampliación busca sumar capacidad de transporte de crudo desde Vaca Muerta.</t>
         </is>
       </c>
       <c r="D4">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Pluspetrol (Argentina); Gas y Petróleo del Neuquén S.A. (Argentina)</t>
+          <t>Oldelval (Argentina)</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Pluspetrol Cuenca Neuquina S.R.L.</t>
+          <t>Oleoductos del Valle SDE</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -682,12 +682,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Upstream</t>
+          <t>Midstream</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Neuquén</t>
+          <t>Neuquén; Río Negro</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -696,10 +696,10 @@
         </is>
       </c>
       <c r="M4">
-        <v>12400</v>
+        <v>380</v>
       </c>
       <c r="N4">
-        <v>12400</v>
+        <v>380</v>
       </c>
       <c r="R4">
         <v>0</v>
@@ -709,72 +709,69 @@
           <t>En evaluación</t>
         </is>
       </c>
-      <c r="T4">
-        <v>6990</v>
-      </c>
       <c r="V4" s="2">
-        <v>45771</v>
+        <v>45859</v>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>Globaris; Gobierno de Neuquén; EconoJournal; Luis Caputo; Clarín; La Nación; Bloomberg</t>
+          <t>Globaris; Oldelval; Infobae; auditoría 2026-08-08</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>https://www.neuqueninforma.gob.ar/noticias/2026/04/23/256641-neuquen-suma-un-nuevo-megaproyecto-al-rigi-con-apoyo-de-gyp; https://econojournal.com.ar/oilgas/pluspetrol-solicito-la-adhesion-al-rigi-para-el-bloque-bajo-del-choique-la-invernada-con-una-inversion-de-us12-000-millones/; https://x.com/LuisCaputoAR/status/2047621135127269495; https://www.clarin.com/economia/rigi-vaca-muerta-pluspetrol-presento-inversiones-us-12000-millones-campo-compro-exxon_0_gYALiNgXD0.html; https://www.lanacion.com.ar/economia/pluspetrol-y-gyp-obtuvieron-el-rigi-para-un-proyecto-de-us12400-millones-en-vaca-muerta-nid02102026/; https://www.bloomberglinea.com/latinoamerica/argentina/pluspetrol-recibe-luz-verde-del-rigi-para-invertir-us12400-millones-en-vaca-muerta/</t>
+          <t>https://www.oldelval.com/oldelval-inicia-la-etapa-constructiva-del-proyecto-duplicar-norte/; https://www.oldelval.com/oldelval-confirmo-la-ejecucion-del-proyecto-duplicar-norte/; https://www.infobae.com/economia/2026/05/13/el-gobierno-aprobo-el-ingreso-al-rigi-de-la-ampliacion-del-gasoducto-perito-moreno-con-una-inversion-de-usd-550-millones/</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Duplicar Norte</t>
+          <t>El Pachón</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Construcción de un oleoducto de aproximadamente 207 km entre el área de Auca Mahuida/Puesto Hernández, en Neuquén, y Allen, en Río Negro, junto con obras de repotenciación y medición. La ampliación busca sumar capacidad de transporte de crudo desde Vaca Muerta.</t>
+          <t>Desarrollo de una mina de cobre y molibdeno de gran escala en San Juan, con plata como subproducto e infraestructura de procesamiento asociada. La solicitud al RIGI corresponde a la primera fase del proyecto y está orientada a producción para exportación.</t>
         </is>
       </c>
       <c r="D5">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Oldelval (Argentina)</t>
+          <t>Glencore (Suiza)</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Oleoductos del Valle SDE</t>
+          <t>Glencore Pachón S.A.</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Petróleo y Gas</t>
+          <t>Minería</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Midstream</t>
+          <t>Cobre</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Neuquén; Río Negro</t>
+          <t>San Juan</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>Patagonia</t>
+          <t>Cuyo</t>
         </is>
       </c>
       <c r="M5">
-        <v>380</v>
+        <v>9500</v>
       </c>
       <c r="N5">
-        <v>380</v>
+        <v>9500</v>
       </c>
       <c r="R5">
         <v>0</v>
@@ -785,68 +782,68 @@
         </is>
       </c>
       <c r="V5" s="2">
-        <v>45859</v>
+        <v>45887</v>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>Globaris; Oldelval; Infobae; auditoría 2026-08-08</t>
+          <t>Globaris; Glencore; Luis Caputo; Reuters; Infobae; auditoría 2026-08-08</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>https://www.oldelval.com/oldelval-inicia-la-etapa-constructiva-del-proyecto-duplicar-norte/; https://www.oldelval.com/oldelval-confirmo-la-ejecucion-del-proyecto-duplicar-norte/; https://www.infobae.com/economia/2026/05/13/el-gobierno-aprobo-el-ingreso-al-rigi-de-la-ampliacion-del-gasoducto-perito-moreno-con-una-inversion-de-usd-550-millones/</t>
+          <t>https://www.glencore.com/media-and-insights/news/glencore-submits-RIGI-applications-in-respect-of-its-argentine-copper-projects; https://x.com/LuisCaputoAR/status/1957458679835594969; https://www.reuters.com/latam/negocio/7X5ZW2SXG5IYNBUILMTT6GMS6U-2025-08-21/; https://www.infobae.com/economia/2026/05/13/el-gobierno-aprobo-el-ingreso-al-rigi-de-la-ampliacion-del-gasoducto-perito-moreno-con-una-inversion-de-usd-550-millones/</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>El Pachón</t>
+          <t>El Trapial</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Desarrollo de una mina de cobre y molibdeno de gran escala en San Juan, con plata como subproducto e infraestructura de procesamiento asociada. La solicitud al RIGI corresponde a la primera fase del proyecto y está orientada a producción para exportación.</t>
+          <t>Desarrollo de petróleo no convencional en el área El Trapial Este, en la formación Vaca Muerta, provincia de Neuquén. El programa prevé perforación, completación e infraestructura de superficie para ampliar la producción del bloque.</t>
         </is>
       </c>
       <c r="D6">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Glencore (Suiza)</t>
+          <t>Chevron (Estados Unidos)</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Glencore Pachón S.A.</t>
+          <t>Chevron</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Minería</t>
+          <t>Petróleo y Gas</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Cobre</t>
+          <t>Upstream</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>San Juan</t>
+          <t>Neuquén</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>Cuyo</t>
+          <t>Patagonia</t>
         </is>
       </c>
       <c r="M6">
-        <v>9500</v>
+        <v>13800</v>
       </c>
       <c r="N6">
-        <v>9500</v>
+        <v>13800</v>
       </c>
       <c r="R6">
         <v>0</v>
@@ -857,68 +854,68 @@
         </is>
       </c>
       <c r="V6" s="2">
-        <v>45887</v>
+        <v>46175</v>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>Globaris; Glencore; Luis Caputo; Reuters; Infobae; auditoría 2026-08-08</t>
+          <t>Globaris; Chevron; Infobae; Clarín; auditoría 2026-08-08</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>https://www.glencore.com/media-and-insights/news/glencore-submits-RIGI-applications-in-respect-of-its-argentine-copper-projects; https://x.com/LuisCaputoAR/status/1957458679835594969; https://www.reuters.com/latam/negocio/7X5ZW2SXG5IYNBUILMTT6GMS6U-2025-08-21/; https://www.infobae.com/economia/2026/05/13/el-gobierno-aprobo-el-ingreso-al-rigi-de-la-ampliacion-del-gasoducto-perito-moreno-con-una-inversion-de-usd-550-millones/</t>
+          <t>https://www.chevron.com/worldwide/argentina; https://www.infobae.com/economia/2026/06/02/chevron-presento-un-megaproyecto-bajo-el-rigi-para-invertir-usd-13800-millones-en-vaca-muerta/; https://www.clarin.com/economia/megainversion-vaca-muerta-chevron-presento-pedido-rigi-us-13800-millones_0_EXuEOYbjiy.html</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>El Trapial</t>
+          <t>NCA+ (Nuevo Central Argentino)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Desarrollo de petróleo no convencional en el área El Trapial Este, en la formación Vaca Muerta, provincia de Neuquén. El programa prevé perforación, completación e infraestructura de superficie para ampliar la producción del bloque.</t>
+          <t>Programa de inversión ferroviaria de carga de Nuevo Central Argentino para mejorar infraestructura y capacidad operativa de la red que vincula centros productivos con puertos de exportación. El proyecto alcanza tramos en Buenos Aires, Santa Fe, Santiago del Estero y Chaco.</t>
         </is>
       </c>
       <c r="D7">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Chevron (Estados Unidos)</t>
+          <t>Nuevo Central Argentino S.A. (Argentina)</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Chevron</t>
+          <t>Nuevo Central Argentino S.A.</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Petróleo y Gas</t>
+          <t>Infraestructura</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Upstream</t>
+          <t>Ferroviario</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>Neuquén</t>
+          <t>Buenos Aires; Santa Fe; Santiago del Estero; Chaco</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>Patagonia</t>
+          <t>Múltiples</t>
         </is>
       </c>
       <c r="M7">
-        <v>13800</v>
+        <v>200</v>
       </c>
       <c r="N7">
-        <v>13800</v>
+        <v>200</v>
       </c>
       <c r="R7">
         <v>0</v>
@@ -928,69 +925,66 @@
           <t>En evaluación</t>
         </is>
       </c>
-      <c r="V7" s="2">
-        <v>46175</v>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>Globaris; Chevron; Infobae; Clarín; auditoría 2026-08-08</t>
+          <t>Globaris; Ministerio de Economía / Boletín Oficial; Nuevo Central Argentino; Infobae; auditoría 2026-08-08</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>https://www.chevron.com/worldwide/argentina; https://www.infobae.com/economia/2026/06/02/chevron-presento-un-megaproyecto-bajo-el-rigi-para-invertir-usd-13800-millones-en-vaca-muerta/; https://www.clarin.com/economia/megainversion-vaca-muerta-chevron-presento-pedido-rigi-us-13800-millones_0_EXuEOYbjiy.html</t>
+          <t>https://www.argentina.gob.ar/normativa/nacional/resoluci%C3%B3n-39-2025-415411/texto; https://www.nca.com.ar/Nuestra-red; https://www.infobae.com/economia/2026/05/13/el-gobierno-aprobo-el-ingreso-al-rigi-de-la-ampliacion-del-gasoducto-perito-moreno-con-una-inversion-de-usd-550-millones/</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>NCA+ (Nuevo Central Argentino)</t>
+          <t>Parque Eólico La Rinconada</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Programa de inversión ferroviaria de carga de Nuevo Central Argentino para mejorar infraestructura y capacidad operativa de la red que vincula centros productivos con puertos de exportación. El proyecto alcanza tramos en Buenos Aires, Santa Fe, Santiago del Estero y Chaco.</t>
+          <t>Construcción de un parque eólico de 94,5 MW en Olavarría, provincia de Buenos Aires, integrado por 21 aerogeneradores. La energía se destinará principalmente a abastecer la planta siderúrgica de Siderca en Campana.</t>
         </is>
       </c>
       <c r="D8">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Nuevo Central Argentino S.A. (Argentina)</t>
+          <t>Tenaris (Argentina)</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Nuevo Central Argentino S.A.</t>
+          <t>Vientos La Rinconada S.A.U.</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Infraestructura</t>
+          <t>Energía</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Ferroviario</t>
+          <t>Eólico</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>Buenos Aires; Santa Fe; Santiago del Estero; Chaco</t>
+          <t>Buenos Aires</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>Múltiples</t>
+          <t>Centro</t>
         </is>
       </c>
       <c r="M8">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="N8">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="R8">
         <v>0</v>
@@ -1000,66 +994,69 @@
           <t>En evaluación</t>
         </is>
       </c>
+      <c r="V8" s="2">
+        <v>45805</v>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>Globaris; Ministerio de Economía / Boletín Oficial; Nuevo Central Argentino; Infobae; auditoría 2026-08-08</t>
+          <t>Globaris; Tenaris; Infobae; auditoría 2026-08-08</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>https://www.argentina.gob.ar/normativa/nacional/resoluci%C3%B3n-39-2025-415411/texto; https://www.nca.com.ar/Nuestra-red; https://www.infobae.com/economia/2026/05/13/el-gobierno-aprobo-el-ingreso-al-rigi-de-la-ampliacion-del-gasoducto-perito-moreno-con-una-inversion-de-usd-550-millones/</t>
+          <t>https://www.tenaris.com/en/news/2025/tenaris-begins-construction-of-second-wind-farm-in-argentina; https://www.infobae.com/economia/2026/05/13/el-gobierno-aprobo-el-ingreso-al-rigi-de-la-ampliacion-del-gasoducto-perito-moreno-con-una-inversion-de-usd-550-millones/</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Parque Eólico La Rinconada</t>
+          <t>Pozuelos Pastos Grandes (PPG)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Construcción de un parque eólico de 94,5 MW en Olavarría, provincia de Buenos Aires, integrado por 21 aerogeneradores. La energía se destinará principalmente a abastecer la planta siderúrgica de Siderca en Campana.</t>
+          <t>Desarrollo integrado de litio en los salares Pozuelos y Pastos Grandes, en la Puna salteña, mediante una operación conjunta de Ganfeng Lithium y Lithium Argentina. El plan contempla infraestructura de extracción y procesamiento y una expansión por etapas hasta una capacidad objetivo de 150.000 toneladas anuales de carbonato de litio equivalente.</t>
         </is>
       </c>
       <c r="D9">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Tenaris (Argentina)</t>
+          <t>Ganfeng Lithium (China); Lithium Argentina AG (Suiza)</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vientos La Rinconada S.A.U.</t>
+          <t>Lithea Inc.</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Energía</t>
+          <t>Minería</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Eólico</t>
+          <t>Litio</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>Buenos Aires</t>
+          <t>Salta</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>Centro</t>
+          <t>NOA</t>
         </is>
       </c>
       <c r="M9">
-        <v>206</v>
+        <v>4245</v>
       </c>
       <c r="N9">
-        <v>206</v>
+        <v>4245</v>
       </c>
       <c r="R9">
         <v>0</v>
@@ -1070,41 +1067,41 @@
         </is>
       </c>
       <c r="V9" s="2">
-        <v>45805</v>
+        <v>46081</v>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>Globaris; Tenaris; Infobae; auditoría 2026-08-08</t>
+          <t>Globaris; Gobierno de Salta; Lithium Argentina; Infobae; auditoría 2026-08-08</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>https://www.tenaris.com/en/news/2025/tenaris-begins-construction-of-second-wind-farm-in-argentina; https://www.infobae.com/economia/2026/05/13/el-gobierno-aprobo-el-ingreso-al-rigi-de-la-ampliacion-del-gasoducto-perito-moreno-con-una-inversion-de-usd-550-millones/</t>
+          <t>https://www.salta.gob.ar/prensa/noticias/avanza-en-salta-el-proyecto-de-litio-pozuelos-pastos-grandes-104827; https://investors.lithium-argentina.com/news-releases/news-release-details/lithium-argentina-reports-fourth-quarter-and-full-year-2025; https://www.infobae.com/economia/2026/05/13/el-gobierno-aprobo-el-ingreso-al-rigi-de-la-ampliacion-del-gasoducto-perito-moreno-con-una-inversion-de-usd-550-millones/</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Pozuelos Pastos Grandes (PPG)</t>
+          <t>Sal de Vida</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Desarrollo integrado de litio en los salares Pozuelos y Pastos Grandes, en la Puna salteña, mediante una operación conjunta de Ganfeng Lithium y Lithium Argentina. El plan contempla infraestructura de extracción y procesamiento y una expansión por etapas hasta una capacidad objetivo de 150.000 toneladas anuales de carbonato de litio equivalente.</t>
+          <t>Desarrollo de litio en el Salar del Hombre Muerto, Catamarca, con extracción de salmuera e instalaciones de procesamiento. La primera etapa prevé una capacidad de aproximadamente 15.000 toneladas anuales de carbonato de litio equivalente.</t>
         </is>
       </c>
       <c r="D10">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Ganfeng Lithium (China); Lithium Argentina AG (Suiza)</t>
+          <t>Rio Tinto (Reino Unido)</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lithea Inc.</t>
+          <t>Sal de Vida S.A.</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1119,7 +1116,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>Salta</t>
+          <t>Catamarca</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1128,10 +1125,10 @@
         </is>
       </c>
       <c r="M10">
-        <v>4245</v>
+        <v>818</v>
       </c>
       <c r="N10">
-        <v>4245</v>
+        <v>818</v>
       </c>
       <c r="R10">
         <v>0</v>
@@ -1142,68 +1139,68 @@
         </is>
       </c>
       <c r="V10" s="2">
-        <v>46081</v>
+        <v>45758</v>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>Globaris; Gobierno de Salta; Lithium Argentina; Infobae; auditoría 2026-08-08</t>
+          <t>Globaris; Rio Tinto; Infobae; auditoría 2026-08-08</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>https://www.salta.gob.ar/prensa/noticias/avanza-en-salta-el-proyecto-de-litio-pozuelos-pastos-grandes-104827; https://investors.lithium-argentina.com/news-releases/news-release-details/lithium-argentina-reports-fourth-quarter-and-full-year-2025; https://www.infobae.com/economia/2026/05/13/el-gobierno-aprobo-el-ingreso-al-rigi-de-la-ampliacion-del-gasoducto-perito-moreno-con-una-inversion-de-usd-550-millones/</t>
+          <t>https://www.riotinto.com/en/news/releases/2025/rio-tinto-confirmed-as-preferred-partner-on-world-class-salares-altoandinos-lithium-project; https://www.infobae.com/economia/2025/10/07/hay-mas-de-usd-18000-millones-a-la-espera-de-aprobacion-en-proyectos-del-rigi/; https://www.infobae.com/economia/2026/05/13/el-gobierno-aprobo-el-ingreso-al-rigi-de-la-ampliacion-del-gasoducto-perito-moreno-con-una-inversion-de-usd-550-millones/</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Sal de Vida</t>
+          <t>Loma Jarillosa Este y Puesto Silva Oeste</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Desarrollo de litio en el Salar del Hombre Muerto, Catamarca, con extracción de salmuera e instalaciones de procesamiento. La primera etapa prevé una capacidad de aproximadamente 15.000 toneladas anuales de carbonato de litio equivalente.</t>
+          <t>Desarrollo integrado de petróleo no convencional en los bloques Loma Jarillosa Este y Puesto Silva Oeste, en Vaca Muerta, mediante perforación en modo factoría, una planta central de procesamiento y sistemas compartidos de evacuación. El plan busca elevar la producción conjunta hasta unos 20.000 barriles equivalentes diarios en tres años.</t>
         </is>
       </c>
       <c r="D11">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Rio Tinto (Reino Unido)</t>
+          <t>GeoPark (Colombia); Gas y Petróleo del Neuquén S.A. (Argentina)</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Sal de Vida S.A.</t>
+          <t>GeoPark</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Minería</t>
+          <t>Petróleo y Gas</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Litio</t>
+          <t>Upstream</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>Catamarca</t>
+          <t>Neuquén</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>NOA</t>
+          <t>Patagonia</t>
         </is>
       </c>
       <c r="M11">
-        <v>818</v>
+        <v>1000</v>
       </c>
       <c r="N11">
-        <v>818</v>
+        <v>1000</v>
       </c>
       <c r="R11">
         <v>0</v>
@@ -1214,68 +1211,68 @@
         </is>
       </c>
       <c r="V11" s="2">
-        <v>45758</v>
+        <v>46157</v>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>Globaris; Rio Tinto; Infobae; auditoría 2026-08-08</t>
+          <t>Globaris; GeoPark; EconoJournal; auditoría 2026-08-08</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>https://www.riotinto.com/en/news/releases/2025/rio-tinto-confirmed-as-preferred-partner-on-world-class-salares-altoandinos-lithium-project; https://www.infobae.com/economia/2025/10/07/hay-mas-de-usd-18000-millones-a-la-espera-de-aprobacion-en-proyectos-del-rigi/; https://www.infobae.com/economia/2026/05/13/el-gobierno-aprobo-el-ingreso-al-rigi-de-la-ampliacion-del-gasoducto-perito-moreno-con-una-inversion-de-usd-550-millones/</t>
+          <t>https://www.geo-park.com/es/news/geopark-solicita-adhesion-al-rigi-por-proyecto-de-inversion/; https://econojournal.com.ar/oilgas/geopark-presenta-al-rigi-una-inversion-por-us1-000-millones-para-un-hub-petrolero-en-vaca-muerta/</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Loma Jarillosa Este y Puesto Silva Oeste</t>
+          <t>Minera Agua Rica (MARA)</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Desarrollo integrado de petróleo no convencional en los bloques Loma Jarillosa Este y Puesto Silva Oeste, en Vaca Muerta, mediante perforación en modo factoría, una planta central de procesamiento y sistemas compartidos de evacuación. El plan busca elevar la producción conjunta hasta unos 20.000 barriles equivalentes diarios en tres años.</t>
+          <t>Desarrollo de una mina de cobre, oro, plata y molibdeno en Catamarca, integrando el yacimiento Agua Rica con la infraestructura existente de Alumbrera, ubicada a unos 35 km. El esquema MARA contempla explotación, procesamiento y uso de instalaciones compartidas para producción destinada principalmente a exportación.</t>
         </is>
       </c>
       <c r="D12">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>GeoPark (Colombia); Gas y Petróleo del Neuquén S.A. (Argentina)</t>
+          <t>Glencore (Suiza)</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>GeoPark</t>
+          <t>Minera Agua Rica LLC Sucursal Argentina</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Petróleo y Gas</t>
+          <t>Minería</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Upstream</t>
+          <t>Cobre</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>Neuquén</t>
+          <t>Catamarca</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>Patagonia</t>
+          <t>NOA</t>
         </is>
       </c>
       <c r="M12">
-        <v>1000</v>
+        <v>4000</v>
       </c>
       <c r="N12">
-        <v>1000</v>
+        <v>4000</v>
       </c>
       <c r="R12">
         <v>0</v>
@@ -1286,41 +1283,41 @@
         </is>
       </c>
       <c r="V12" s="2">
-        <v>46157</v>
+        <v>45887</v>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>Globaris; GeoPark; EconoJournal; auditoría 2026-08-08</t>
+          <t>Globaris; Glencore; Luis Caputo; Reuters; Infobae; auditoría 2026-08-08</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>https://www.geo-park.com/es/news/geopark-solicita-adhesion-al-rigi-por-proyecto-de-inversion/; https://econojournal.com.ar/oilgas/geopark-presenta-al-rigi-una-inversion-por-us1-000-millones-para-un-hub-petrolero-en-vaca-muerta/</t>
+          <t>https://www.glencore.com/media-and-insights/news/glencore-submits-RIGI-applications-in-respect-of-its-argentine-copper-projects; https://x.com/LuisCaputoAR/status/1957458679835594969; https://www.reuters.com/latam/negocio/7X5ZW2SXG5IYNBUILMTT6GMS6U-2025-08-21/; https://www.infobae.com/economia/2026/05/13/el-gobierno-aprobo-el-ingreso-al-rigi-de-la-ampliacion-del-gasoducto-perito-moreno-con-una-inversion-de-usd-550-millones/</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Minera Agua Rica (MARA)</t>
+          <t>Jama Solaroz</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Desarrollo de una mina de cobre, oro, plata y molibdeno en Catamarca, integrando el yacimiento Agua Rica con la infraestructura existente de Alumbrera, ubicada a unos 35 km. El esquema MARA contempla explotación, procesamiento y uso de instalaciones compartidas para producción destinada principalmente a exportación.</t>
+          <t>Desarrollo integrado de litio en los proyectos Jama y Solaroz, en la Puna de Jujuy, con una planta prevista en el Salar de Jama. La iniciativa contempla extracción de salmuera y producción de compuestos de litio, con una capacidad informada de aproximadamente 22.000 toneladas anuales.</t>
         </is>
       </c>
       <c r="D13">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Glencore (Suiza)</t>
+          <t>CNGR Advanced Material Co., Ltd. (China)</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Minera Agua Rica LLC Sucursal Argentina</t>
+          <t>CNGR Advanced Material Co., Ltd.</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1330,12 +1327,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Cobre</t>
+          <t>Litio</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>Catamarca</t>
+          <t>Jujuy</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -1344,10 +1341,10 @@
         </is>
       </c>
       <c r="M13">
-        <v>4000</v>
+        <v>1151</v>
       </c>
       <c r="N13">
-        <v>4000</v>
+        <v>1151</v>
       </c>
       <c r="R13">
         <v>0</v>
@@ -1358,68 +1355,68 @@
         </is>
       </c>
       <c r="V13" s="2">
-        <v>45887</v>
+        <v>46111</v>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>Globaris; Glencore; Luis Caputo; Reuters; Infobae; auditoría 2026-08-08</t>
+          <t>Globaris; Gobierno de Jujuy; El Tribuno de Jujuy; Infobae; auditoría 2026-08-08</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>https://www.glencore.com/media-and-insights/news/glencore-submits-RIGI-applications-in-respect-of-its-argentine-copper-projects; https://x.com/LuisCaputoAR/status/1957458679835594969; https://www.reuters.com/latam/negocio/7X5ZW2SXG5IYNBUILMTT6GMS6U-2025-08-21/; https://www.infobae.com/economia/2026/05/13/el-gobierno-aprobo-el-ingreso-al-rigi-de-la-ampliacion-del-gasoducto-perito-moreno-con-una-inversion-de-usd-550-millones/</t>
+          <t>https://prensa.jujuy.gob.ar/jujuy/jujuy-se-afianza-como-productor-minerales-criticos-el-desarrollo-la-transicion-energetica-n120116; https://eltribunodejujuy.com/informacion-general/2026-4-1-0-0-0-proyecto-de-litio-en-jujuy-busca-la-adhesion-al-rigi; https://www.infobae.com/economia/2026/05/13/el-gobierno-aprobo-el-ingreso-al-rigi-de-la-ampliacion-del-gasoducto-perito-moreno-con-una-inversion-de-usd-550-millones/</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Jama Solaroz</t>
+          <t>LLL Oil</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Desarrollo integrado de litio en los proyectos Jama y Solaroz, en la Puna de Jujuy, con una planta prevista en el Salar de Jama. La iniciativa contempla extracción de salmuera y producción de compuestos de litio, con una capacidad informada de aproximadamente 22.000 toneladas anuales.</t>
+          <t>Desarrollo integrado de cinco bloques contiguos de petróleo no convencional en Vaca Muerta: La Angostura Norte, La Angostura Sur I, La Angostura Sur II, La Angostura Suroeste y Barreal Grande. El programa prevé perforar 1.152 pozos y compartir instalaciones de superficie y servicios para alcanzar una producción aproximada de 240.000 barriles diarios hacia 2032, destinada a exportación.</t>
         </is>
       </c>
       <c r="D14">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>CNGR Advanced Material Co., Ltd. (China)</t>
+          <t>YPF S.A. (Argentina)</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>CNGR Advanced Material Co., Ltd.</t>
+          <t>YPF</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Minería</t>
+          <t>Petróleo y Gas</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Litio</t>
+          <t>Upstream</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>Jujuy</t>
+          <t>Neuquén</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>NOA</t>
+          <t>Patagonia</t>
         </is>
       </c>
       <c r="M14">
-        <v>1151</v>
+        <v>25000</v>
       </c>
       <c r="N14">
-        <v>1151</v>
+        <v>25000</v>
       </c>
       <c r="R14">
         <v>0</v>
@@ -1430,41 +1427,41 @@
         </is>
       </c>
       <c r="V14" s="2">
-        <v>46111</v>
+        <v>46157</v>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>Globaris; Gobierno de Jujuy; El Tribuno de Jujuy; Infobae; auditoría 2026-08-08</t>
+          <t>Globaris; YPF; EconoJournal; Reuters; auditoría 2026-08-08</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>https://prensa.jujuy.gob.ar/jujuy/jujuy-se-afianza-como-productor-minerales-criticos-el-desarrollo-la-transicion-energetica-n120116; https://eltribunodejujuy.com/informacion-general/2026-4-1-0-0-0-proyecto-de-litio-en-jujuy-busca-la-adhesion-al-rigi; https://www.infobae.com/economia/2026/05/13/el-gobierno-aprobo-el-ingreso-al-rigi-de-la-ampliacion-del-gasoducto-perito-moreno-con-una-inversion-de-usd-550-millones/</t>
+          <t>https://www.instagram.com/p/DYX1JXjj-bC/; https://econojournal.com.ar/destacada/ypf-presento-rigi-acelerar-produccion-petroleo-vaca-muerta/; https://www.reuters.com/business/energy/argentinas-ypf-registers-25-bln-oil-project-rigi-investment-scheme-2026-05-15/</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>LLL Oil</t>
+          <t>Bandurria Norte</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Desarrollo integrado de cinco bloques contiguos de petróleo no convencional en Vaca Muerta: La Angostura Norte, La Angostura Sur I, La Angostura Sur II, La Angostura Suroeste y Barreal Grande. El programa prevé perforar 1.152 pozos y compartir instalaciones de superficie y servicios para alcanzar una producción aproximada de 240.000 barriles diarios hacia 2032, destinada a exportación.</t>
+          <t>Desarrollo greenfield de petróleo no convencional en Bandurria Norte, Vaca Muerta, sobre una superficie aproximada de 26.500 acres. El plan contempla 332 pozos horizontales, planta de tratamiento de crudo, compresión de gas, redes de recolección y ductos, con una meta de 50.000 barriles equivalentes diarios.</t>
         </is>
       </c>
       <c r="D15">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>YPF S.A. (Argentina)</t>
+          <t>Vista Energy (Argentina)</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>YPF</t>
+          <t>Vista Energy</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1488,10 +1485,10 @@
         </is>
       </c>
       <c r="M15">
-        <v>25000</v>
+        <v>5800</v>
       </c>
       <c r="N15">
-        <v>25000</v>
+        <v>5800</v>
       </c>
       <c r="R15">
         <v>0</v>
@@ -1502,41 +1499,41 @@
         </is>
       </c>
       <c r="V15" s="2">
-        <v>46157</v>
+        <v>46224</v>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>Globaris; YPF; EconoJournal; Reuters; auditoría 2026-08-08</t>
+          <t>Globaris; EconoJournal; Vista Energy / SEC; Oil &amp; Gas Journal; auditoría 2026-08-08</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DYX1JXjj-bC/; https://econojournal.com.ar/destacada/ypf-presento-rigi-acelerar-produccion-petroleo-vaca-muerta/; https://www.reuters.com/business/energy/argentinas-ypf-registers-25-bln-oil-project-rigi-investment-scheme-2026-05-15/</t>
+          <t>https://econojournal.com.ar/oilgas/vista-energy-pidio-la-adhesion-al-rigi-para-un-proyecto-de-us-5-800-millones-en-vaca-muerta/; https://www.sec.gov/Archives/edgar/data/1762506/000119312526306139/d151775dex1.htm; https://www.ogj.com/exploration-development/news/55394130/vista-seeks-rigi-approval-for-58-billion-bandurria-norte-development</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Bandurria Norte</t>
+          <t>Argentina LNG</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Desarrollo greenfield de petróleo no convencional en Bandurria Norte, Vaca Muerta, sobre una superficie aproximada de 26.500 acres. El plan contempla 332 pozos horizontales, planta de tratamiento de crudo, compresión de gas, redes de recolección y ductos, con una meta de 50.000 barriles equivalentes diarios.</t>
+          <t>Proyecto integrado de producción y exportación de gas natural licuado: desarrollo de gas rico en Vaca Muerta, infraestructura dedicada de transporte, plantas de procesamiento y fraccionamiento y dos unidades flotantes de licuefacción (FLNG) por 12 MTPA en el Golfo San Matías.</t>
         </is>
       </c>
       <c r="D16">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Vista Energy (Argentina)</t>
+          <t>YPF S.A. (Argentina); Eni S.p.A. (Italia); XRG (Emiratos Árabes Unidos)</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vista Energy</t>
+          <t>YPF</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1546,12 +1543,12 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Upstream</t>
+          <t>Midstream</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>Neuquén</t>
+          <t>Neuquén; Río Negro</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -1560,10 +1557,7 @@
         </is>
       </c>
       <c r="M16">
-        <v>5800</v>
-      </c>
-      <c r="N16">
-        <v>5800</v>
+        <v>51000</v>
       </c>
       <c r="R16">
         <v>0</v>
@@ -1574,274 +1568,205 @@
         </is>
       </c>
       <c r="V16" s="2">
-        <v>46224</v>
+        <v>46247</v>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>Globaris; EconoJournal; Vista Energy / SEC; Oil &amp; Gas Journal; auditoría 2026-08-08</t>
+          <t>YPF / Argentina LNG; La Nación; Infobae; Data Energía</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>https://econojournal.com.ar/oilgas/vista-energy-pidio-la-adhesion-al-rigi-para-un-proyecto-de-us-5-800-millones-en-vaca-muerta/; https://www.sec.gov/Archives/edgar/data/1762506/000119312526306139/d151775dex1.htm; https://www.ogj.com/exploration-development/news/55394130/vista-seeks-rigi-approval-for-58-billion-bandurria-norte-development</t>
+          <t>https://argentina-lng.ypf.com/assets/pdf/ENG-Argentina-LNG-Adhesion-RIGI.pdf; https://www.lanacion.com.ar/economia/un-proyecto-por-us51000-millones-impulsado-por-ypf-solicito-la-adhesion-al-rigi-nid13082026/; https://www.infobae.com/economia/2026/08/13/con-una-inversion-de-usd-50000-millones-ypf-presenta-al-rigi-el-mayor-proyecto-de-su-historia-para-exportar-gas-de-vaca-muerta/; https://dataenergia.ar/gas/argentina-lgn-solicitaron-la-adhesion-formal-al-rigi-para-una-inversion-historica-de-u-s-51-000-millones-202681319370</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Argentina LNG</t>
+          <t>Toyota</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Proyecto integrado de producción y exportación de gas natural licuado: desarrollo de gas rico en Vaca Muerta, infraestructura dedicada de transporte, plantas de procesamiento y fraccionamiento y dos unidades flotantes de licuefacción (FLNG) por 12 MTPA en el Golfo San Matías.</t>
+          <t>Nueva planta dentro del complejo industrial de Toyota en Zárate para producir un vehículo electrificado —descripto por el ministro de Economía como 100% electrificado—, con aproximadamente 70% de la producción destinada a exportación.</t>
         </is>
       </c>
       <c r="D17">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>YPF S.A. (Argentina); Eni S.p.A. (Italia); XRG (Emiratos Árabes Unidos)</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>YPF</t>
+          <t>Toyota Argentina S.A. (Argentina)</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Petróleo y Gas</t>
+          <t>Tecnología</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Midstream</t>
+          <t>Automotriz</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>Neuquén; Río Negro</t>
+          <t>Buenos Aires</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>Patagonia</t>
+          <t>Zárate</t>
         </is>
       </c>
       <c r="M17">
-        <v>51000</v>
-      </c>
-      <c r="R17">
-        <v>0</v>
+        <v>1341</v>
       </c>
       <c r="S17" t="inlineStr">
         <is>
           <t>En evaluación</t>
         </is>
       </c>
+      <c r="T17">
+        <v>6200</v>
+      </c>
       <c r="V17" s="2">
-        <v>46247</v>
+        <v>46295</v>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>YPF / Argentina LNG; La Nación; Infobae; Data Energía</t>
+          <t>Luis Caputo / Ministerio de Economía (X, 30/09/2026); Reuters (30/09/2026); La Nación / Toyota Argentina (30/09/2026); ARCA / Decreto 105/2026 (19/02/2026)</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>https://argentina-lng.ypf.com/assets/pdf/ENG-Argentina-LNG-Adhesion-RIGI.pdf; https://www.lanacion.com.ar/economia/un-proyecto-por-us51000-millones-impulsado-por-ypf-solicito-la-adhesion-al-rigi-nid13082026/; https://www.infobae.com/economia/2026/08/13/con-una-inversion-de-usd-50000-millones-ypf-presenta-al-rigi-el-mayor-proyecto-de-su-historia-para-exportar-gas-de-vaca-muerta/; https://dataenergia.ar/gas/argentina-lgn-solicitaron-la-adhesion-formal-al-rigi-para-una-inversion-historica-de-u-s-51-000-millones-202681319370</t>
+          <t>https://x.com/LuisCaputoAR/status/2105382049758523681; https://www.reuters.com/world/asia-pacific/toyota-invest-134-billion-argentina-production-plant-2026-09-30/; https://www.lanacion.com.ar/autos/toyota-invertira-us1341-millones-para-fabricar-un-nuevo-vehiculo-en-la-argentina-nid30092026/; https://biblioteca.afip.gob.ar/dcp/DEC_C_000749_2024_08_22</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Toyota</t>
+          <t>PAE Cerro Dragón</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Nueva planta dentro del complejo industrial de Toyota en Zárate para producir un vehículo electrificado —descripto por el ministro de Economía como 100% electrificado—, con aproximadamente 70% de la producción destinada a exportación.</t>
+          <t>Desarrollo de recuperación terciaria de petróleo convencional en Cerro Dragón: 22 plantas de inyección de polímeros, perforación de 100 pozos productores e inyectores, adecuación de pozos, intervención de otros 600 pozos productores e infraestructura complementaria de superficie. Producción incremental estimada: 46 millones de barriles de petróleo y 30 BCF de gas natural.</t>
         </is>
       </c>
       <c r="D18">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Toyota Argentina S.A. (Argentina)</t>
+          <t>Pan American Energy (PAE) (Argentina)</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Tecnología</t>
+          <t>Petróleo y Gas</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Automotriz</t>
+          <t>Upstream</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>Buenos Aires</t>
+          <t>Chubut</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>Zárate</t>
+          <t>Área Cerro Dragón, Cuenca del Golfo San Jorge</t>
         </is>
       </c>
       <c r="M18">
-        <v>1341</v>
+        <v>1200</v>
       </c>
       <c r="S18" t="inlineStr">
         <is>
           <t>En evaluación</t>
         </is>
       </c>
-      <c r="T18">
-        <v>6200</v>
-      </c>
       <c r="V18" s="2">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>Luis Caputo / Ministerio de Economía (X, 30/09/2026); Reuters (30/09/2026); La Nación / Toyota Argentina (30/09/2026); ARCA / Decreto 105/2026 (19/02/2026)</t>
+          <t>Gobierno del Chubut (01/10/2026); La Nación / PAE (01/10/2026); Reuters / Luis Caputo (01/10/2026)</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>https://x.com/LuisCaputoAR/status/2105382049758523681; https://www.reuters.com/world/asia-pacific/toyota-invest-134-billion-argentina-production-plant-2026-09-30/; https://www.lanacion.com.ar/autos/toyota-invertira-us1341-millones-para-fabricar-un-nuevo-vehiculo-en-la-argentina-nid30092026/; https://biblioteca.afip.gob.ar/dcp/DEC_C_000749_2024_08_22</t>
+          <t>https://noticias.chubut.gob.ar/notas/gobierno/5481/torres-encabezo-en-la-sede-de-la-ocde-el-anuncio-de-una-inversion-de-usd-1200-millones-de-pae-para-cerro-dragon.html; https://www.lanacion.com.ar/economia/pan-american-energy-busca-ingresar-al-rigi-con-una-inversion-de-us1200-millones-para-revitalizar-nid01102026/; https://www.reuters.com/business/energy/pae-invest-12-billion-argentina-oil-field-minister-says-2026-10-01/</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>PAE Cerro Dragón</t>
+          <t>Pampa Exploración S.A.</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Desarrollo de recuperación terciaria de petróleo convencional en Cerro Dragón: 22 plantas de inyección de polímeros, perforación de 100 pozos productores e inyectores, adecuación de pozos, intervención de otros 600 pozos productores e infraestructura complementaria de superficie. Producción incremental estimada: 46 millones de barriles de petróleo y 30 BCF de gas natural.</t>
+          <t>Desarrollo del depósito Lunahuasi de cobre, oro y plata, actualmente en exploración, con perforaciones y una galería de exploración planificada para avanzar hacia su desarrollo minero</t>
         </is>
       </c>
       <c r="D19">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Pan American Energy (PAE) (Argentina)</t>
+          <t>NGEx Minerals Ltd. (Canadá)</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Pampa Exploración S.A.</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Petróleo y Gas</t>
+          <t>Minería</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Upstream</t>
+          <t>Cobre</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>Chubut</t>
+          <t>San Juan</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>Área Cerro Dragón, Cuenca del Golfo San Jorge</t>
+          <t>Departamento Iglesia; Distrito Vicuña</t>
         </is>
       </c>
       <c r="M19">
-        <v>1200</v>
+        <v>2437</v>
+      </c>
+      <c r="R19">
+        <v>0</v>
       </c>
       <c r="S19" t="inlineStr">
         <is>
           <t>En evaluación</t>
         </is>
       </c>
-      <c r="V19" s="2">
-        <v>46296</v>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>Gobierno del Chubut (01/10/2026); La Nación / PAE (01/10/2026); Reuters / Luis Caputo (01/10/2026)</t>
+          <t>NGEx Minerals, 14/05/2026; Panorama Minero, consulta 02/10/2026</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
-        <is>
-          <t>https://noticias.chubut.gob.ar/notas/gobierno/5481/torres-encabezo-en-la-sede-de-la-ocde-el-anuncio-de-una-inversion-de-usd-1200-millones-de-pae-para-cerro-dragon.html; https://www.lanacion.com.ar/economia/pan-american-energy-busca-ingresar-al-rigi-con-una-inversion-de-us1200-millones-para-revitalizar-nid01102026/; https://www.reuters.com/business/energy/pae-invest-12-billion-argentina-oil-field-minister-says-2026-10-01/</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Pampa Exploración S.A.</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Desarrollo del depósito Lunahuasi de cobre, oro y plata, actualmente en exploración, con perforaciones y una galería de exploración planificada para avanzar hacia su desarrollo minero</t>
-        </is>
-      </c>
-      <c r="D20">
-        <v>44</v>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>NGEx Minerals Ltd. (Canadá)</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>Pampa Exploración S.A.</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>Minería</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>Cobre</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>San Juan</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>Departamento Iglesia; Distrito Vicuña</t>
-        </is>
-      </c>
-      <c r="M20">
-        <v>2437</v>
-      </c>
-      <c r="R20">
-        <v>0</v>
-      </c>
-      <c r="S20" t="inlineStr">
-        <is>
-          <t>En evaluación</t>
-        </is>
-      </c>
-      <c r="AA20" t="inlineStr">
-        <is>
-          <t>NGEx Minerals, 14/05/2026; Panorama Minero, consulta 02/10/2026</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
         <is>
           <t>https://ngexminerals.com/news/ngex-releases-2025-sustainability-summary-122811/; https://www.panorama-minero.com/es/mining-compendium/argentina/project/lunahuasi</t>
         </is>

--- a/downloads/base_interactiva_pendientes.xlsx
+++ b/downloads/base_interactiva_pendientes.xlsx
@@ -356,7 +356,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AB19"/>
+  <dimension ref="A1:AB20"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="21" max="21" width="20.7109375" style="2" customWidth="1"/>
@@ -554,9 +554,6 @@
       <c r="M2">
         <v>726</v>
       </c>
-      <c r="N2">
-        <v>726</v>
-      </c>
       <c r="R2">
         <v>0</v>
       </c>
@@ -626,9 +623,6 @@
       <c r="M3">
         <v>232</v>
       </c>
-      <c r="N3">
-        <v>232</v>
-      </c>
       <c r="R3">
         <v>0</v>
       </c>
@@ -698,9 +692,6 @@
       <c r="M4">
         <v>380</v>
       </c>
-      <c r="N4">
-        <v>380</v>
-      </c>
       <c r="R4">
         <v>0</v>
       </c>
@@ -770,9 +761,6 @@
       <c r="M5">
         <v>9500</v>
       </c>
-      <c r="N5">
-        <v>9500</v>
-      </c>
       <c r="R5">
         <v>0</v>
       </c>
@@ -842,9 +830,6 @@
       <c r="M6">
         <v>13800</v>
       </c>
-      <c r="N6">
-        <v>13800</v>
-      </c>
       <c r="R6">
         <v>0</v>
       </c>
@@ -914,9 +899,6 @@
       <c r="M7">
         <v>200</v>
       </c>
-      <c r="N7">
-        <v>200</v>
-      </c>
       <c r="R7">
         <v>0</v>
       </c>
@@ -983,9 +965,6 @@
       <c r="M8">
         <v>206</v>
       </c>
-      <c r="N8">
-        <v>206</v>
-      </c>
       <c r="R8">
         <v>0</v>
       </c>
@@ -1055,9 +1034,6 @@
       <c r="M9">
         <v>4245</v>
       </c>
-      <c r="N9">
-        <v>4245</v>
-      </c>
       <c r="R9">
         <v>0</v>
       </c>
@@ -1127,9 +1103,6 @@
       <c r="M10">
         <v>818</v>
       </c>
-      <c r="N10">
-        <v>818</v>
-      </c>
       <c r="R10">
         <v>0</v>
       </c>
@@ -1199,9 +1172,6 @@
       <c r="M11">
         <v>1000</v>
       </c>
-      <c r="N11">
-        <v>1000</v>
-      </c>
       <c r="R11">
         <v>0</v>
       </c>
@@ -1271,9 +1241,6 @@
       <c r="M12">
         <v>4000</v>
       </c>
-      <c r="N12">
-        <v>4000</v>
-      </c>
       <c r="R12">
         <v>0</v>
       </c>
@@ -1343,9 +1310,6 @@
       <c r="M13">
         <v>1151</v>
       </c>
-      <c r="N13">
-        <v>1151</v>
-      </c>
       <c r="R13">
         <v>0</v>
       </c>
@@ -1415,9 +1379,6 @@
       <c r="M14">
         <v>25000</v>
       </c>
-      <c r="N14">
-        <v>25000</v>
-      </c>
       <c r="R14">
         <v>0</v>
       </c>
@@ -1487,9 +1448,6 @@
       <c r="M15">
         <v>5800</v>
       </c>
-      <c r="N15">
-        <v>5800</v>
-      </c>
       <c r="R15">
         <v>0</v>
       </c>
@@ -1584,174 +1542,173 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Toyota</t>
+          <t>PAE Cerro Dragón</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Nueva planta dentro del complejo industrial de Toyota en Zárate para producir un vehículo electrificado —descripto por el ministro de Economía como 100% electrificado—, con aproximadamente 70% de la producción destinada a exportación.</t>
+          <t>Desarrollo de recuperación terciaria de petróleo convencional en Cerro Dragón: 22 plantas de inyección de polímeros, perforación de 100 pozos productores e inyectores, adecuación de pozos, intervención de otros 600 pozos productores e infraestructura complementaria de superficie. Producción incremental estimada: 46 millones de barriles de petróleo y 30 BCF de gas natural.</t>
         </is>
       </c>
       <c r="D17">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Toyota Argentina S.A. (Argentina)</t>
+          <t>Pan American Energy (PAE) (Argentina)</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Tecnología</t>
+          <t>Petróleo y Gas</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Automotriz</t>
+          <t>Upstream</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>Buenos Aires</t>
+          <t>Chubut</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>Zárate</t>
+          <t>Área Cerro Dragón, Cuenca del Golfo San Jorge</t>
         </is>
       </c>
       <c r="M17">
-        <v>1341</v>
+        <v>1200</v>
       </c>
       <c r="S17" t="inlineStr">
         <is>
           <t>En evaluación</t>
         </is>
       </c>
-      <c r="T17">
-        <v>6200</v>
-      </c>
       <c r="V17" s="2">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>Luis Caputo / Ministerio de Economía (X, 30/09/2026); Reuters (30/09/2026); La Nación / Toyota Argentina (30/09/2026); ARCA / Decreto 105/2026 (19/02/2026)</t>
+          <t>Gobierno del Chubut (01/10/2026); La Nación / PAE (01/10/2026); Reuters / Luis Caputo (01/10/2026)</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>https://x.com/LuisCaputoAR/status/2105382049758523681; https://www.reuters.com/world/asia-pacific/toyota-invest-134-billion-argentina-production-plant-2026-09-30/; https://www.lanacion.com.ar/autos/toyota-invertira-us1341-millones-para-fabricar-un-nuevo-vehiculo-en-la-argentina-nid30092026/; https://biblioteca.afip.gob.ar/dcp/DEC_C_000749_2024_08_22</t>
+          <t>https://noticias.chubut.gob.ar/notas/gobierno/5481/torres-encabezo-en-la-sede-de-la-ocde-el-anuncio-de-una-inversion-de-usd-1200-millones-de-pae-para-cerro-dragon.html; https://www.lanacion.com.ar/economia/pan-american-energy-busca-ingresar-al-rigi-con-una-inversion-de-us1200-millones-para-revitalizar-nid01102026/; https://www.reuters.com/business/energy/pae-invest-12-billion-argentina-oil-field-minister-says-2026-10-01/</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>PAE Cerro Dragón</t>
+          <t>Pampa Exploración S.A.</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Desarrollo de recuperación terciaria de petróleo convencional en Cerro Dragón: 22 plantas de inyección de polímeros, perforación de 100 pozos productores e inyectores, adecuación de pozos, intervención de otros 600 pozos productores e infraestructura complementaria de superficie. Producción incremental estimada: 46 millones de barriles de petróleo y 30 BCF de gas natural.</t>
+          <t>Desarrollo del depósito Lunahuasi de cobre, oro y plata, actualmente en exploración, con perforaciones y una galería de exploración planificada para avanzar hacia su desarrollo minero</t>
         </is>
       </c>
       <c r="D18">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Pan American Energy (PAE) (Argentina)</t>
+          <t>NGEx Minerals Ltd. (Canadá)</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Pampa Exploración S.A.</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Petróleo y Gas</t>
+          <t>Minería</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Upstream</t>
+          <t>Cobre</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>Chubut</t>
+          <t>San Juan</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>Área Cerro Dragón, Cuenca del Golfo San Jorge</t>
+          <t>Departamento Iglesia; Distrito Vicuña</t>
         </is>
       </c>
       <c r="M18">
-        <v>1200</v>
+        <v>2437</v>
+      </c>
+      <c r="R18">
+        <v>0</v>
       </c>
       <c r="S18" t="inlineStr">
         <is>
           <t>En evaluación</t>
         </is>
       </c>
-      <c r="V18" s="2">
-        <v>46296</v>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>Gobierno del Chubut (01/10/2026); La Nación / PAE (01/10/2026); Reuters / Luis Caputo (01/10/2026)</t>
+          <t>NGEx Minerals, 14/05/2026; Panorama Minero, consulta 02/10/2026</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>https://noticias.chubut.gob.ar/notas/gobierno/5481/torres-encabezo-en-la-sede-de-la-ocde-el-anuncio-de-una-inversion-de-usd-1200-millones-de-pae-para-cerro-dragon.html; https://www.lanacion.com.ar/economia/pan-american-energy-busca-ingresar-al-rigi-con-una-inversion-de-us1200-millones-para-revitalizar-nid01102026/; https://www.reuters.com/business/energy/pae-invest-12-billion-argentina-oil-field-minister-says-2026-10-01/</t>
+          <t>https://ngexminerals.com/news/ngex-releases-2025-sustainability-summary-122811/; https://www.panorama-minero.com/es/mining-compendium/argentina/project/lunahuasi</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Pampa Exploración S.A.</t>
+          <t>Procesamiento de NGLs en Tratayén</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Desarrollo del depósito Lunahuasi de cobre, oro y plata, actualmente en exploración, con perforaciones y una galería de exploración planificada para avanzar hacia su desarrollo minero</t>
+          <t>Construcción de un gasoducto de segregación de corrientes de aproximadamente 100 km y nuevas instalaciones de procesamiento en Tratayén, con capacidad para 43 millones de m³ diarios, para separar líquidos del gas natural. Integra un paquete de dos proyectos de TGS con inversión conjunta superior a USD 3.200 millones; el monto actualizado por VPU no fue publicado.</t>
         </is>
       </c>
       <c r="D19">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>NGEx Minerals Ltd. (Canadá)</t>
+          <t>Transportadora de Gas del Sur S.A. (TGS) (Argentina)</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Pampa Exploración S.A.</t>
+          <t>Procesadora de Gas del Sur S.A. (PGS)</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Minería</t>
+          <t>Petróleo y Gas</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Cobre</t>
+          <t>Midstream</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>San Juan</t>
+          <t>Neuquén</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>Departamento Iglesia; Distrito Vicuña</t>
-        </is>
-      </c>
-      <c r="M19">
-        <v>2437</v>
+          <t>Tratayén, Neuquén</t>
+        </is>
       </c>
       <c r="R19">
         <v>0</v>
@@ -1763,12 +1720,75 @@
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>NGEx Minerals, 14/05/2026; Panorama Minero, consulta 02/10/2026</t>
+          <t>Luis Caputo / Ministerio de Economía (X, 19/10/2026); Shale24 (19/10/2026); TGS, estados financieros 2T 2026 (04/08/2026)</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>https://ngexminerals.com/news/ngex-releases-2025-sustainability-summary-122811/; https://www.panorama-minero.com/es/mining-compendium/argentina/project/lunahuasi</t>
+          <t>https://x.com/LuisCaputoAR/status/2112170371310858454; https://www.shale24.com/oil-gas/tgs-entra-rigi-us-3200-millones-bahia-blanca-ya-suma-dos-obras-liquidos-vaca-muerta-regimen-n1864; https://api.mziq.com/mzfilemanager/v2/d/78ce1f91-b610-429f-b020-add32c211c1f/dcfe21a3-8a28-44d7-5aeb-2e1a49a861e2?origin=2</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Poliducto Tratayén–Bahía Blanca y complejo NGL Puerto Galván</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Construcción de un poliducto de 577 km desde Tratayén hasta Bahía Blanca, una planta de fraccionamiento, instalaciones de almacenamiento y obras en la terminal marítima de Puerto Galván para exportar aproximadamente 2,7 millones de toneladas anuales de propano, butano y gasolina natural. Integra un paquete de dos proyectos de TGS con inversión conjunta superior a USD 3.200 millones; el monto actualizado por VPU no fue publicado.</t>
+        </is>
+      </c>
+      <c r="D20">
+        <v>46</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Transportadora de Gas del Sur S.A. (TGS) (Argentina)</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Midstream de Gas del Sur S.A. (MGS)</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Petróleo y Gas</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>Midstream</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Neuquén; Buenos Aires</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>Tratayén–Bahía Blanca / Puerto Galván</t>
+        </is>
+      </c>
+      <c r="R20">
+        <v>0</v>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>En evaluación</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>Luis Caputo / Ministerio de Economía (X, 19/10/2026); Shale24 (19/10/2026); TGS, estados financieros 2T 2026 (04/08/2026)</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>https://x.com/LuisCaputoAR/status/2112170371310858454; https://www.shale24.com/oil-gas/tgs-entra-rigi-us-3200-millones-bahia-blanca-ya-suma-dos-obras-liquidos-vaca-muerta-regimen-n1864; https://api.mziq.com/mzfilemanager/v2/d/78ce1f91-b610-429f-b020-add32c211c1f/dcfe21a3-8a28-44d7-5aeb-2e1a49a861e2?origin=2</t>
         </is>
       </c>
     </row>

--- a/downloads/base_interactiva_pendientes.xlsx
+++ b/downloads/base_interactiva_pendientes.xlsx
@@ -356,7 +356,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AB20"/>
+  <dimension ref="A1:AB19"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="21" max="21" width="20.7109375" style="2" customWidth="1"/>
@@ -554,9 +554,6 @@
       <c r="M2">
         <v>726</v>
       </c>
-      <c r="R2">
-        <v>0</v>
-      </c>
       <c r="S2" t="inlineStr">
         <is>
           <t>En evaluación</t>
@@ -623,9 +620,6 @@
       <c r="M3">
         <v>232</v>
       </c>
-      <c r="R3">
-        <v>0</v>
-      </c>
       <c r="S3" t="inlineStr">
         <is>
           <t>En evaluación</t>
@@ -692,9 +686,6 @@
       <c r="M4">
         <v>380</v>
       </c>
-      <c r="R4">
-        <v>0</v>
-      </c>
       <c r="S4" t="inlineStr">
         <is>
           <t>En evaluación</t>
@@ -761,9 +752,6 @@
       <c r="M5">
         <v>9500</v>
       </c>
-      <c r="R5">
-        <v>0</v>
-      </c>
       <c r="S5" t="inlineStr">
         <is>
           <t>En evaluación</t>
@@ -828,10 +816,7 @@
         </is>
       </c>
       <c r="M6">
-        <v>13800</v>
-      </c>
-      <c r="R6">
-        <v>0</v>
+        <v>9500</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -899,9 +884,6 @@
       <c r="M7">
         <v>200</v>
       </c>
-      <c r="R7">
-        <v>0</v>
-      </c>
       <c r="S7" t="inlineStr">
         <is>
           <t>En evaluación</t>
@@ -965,9 +947,6 @@
       <c r="M8">
         <v>206</v>
       </c>
-      <c r="R8">
-        <v>0</v>
-      </c>
       <c r="S8" t="inlineStr">
         <is>
           <t>En evaluación</t>
@@ -1034,9 +1013,6 @@
       <c r="M9">
         <v>4245</v>
       </c>
-      <c r="R9">
-        <v>0</v>
-      </c>
       <c r="S9" t="inlineStr">
         <is>
           <t>En evaluación</t>
@@ -1103,9 +1079,6 @@
       <c r="M10">
         <v>818</v>
       </c>
-      <c r="R10">
-        <v>0</v>
-      </c>
       <c r="S10" t="inlineStr">
         <is>
           <t>En evaluación</t>
@@ -1172,9 +1145,6 @@
       <c r="M11">
         <v>1000</v>
       </c>
-      <c r="R11">
-        <v>0</v>
-      </c>
       <c r="S11" t="inlineStr">
         <is>
           <t>En evaluación</t>
@@ -1197,25 +1167,25 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Minera Agua Rica (MARA)</t>
+          <t>Jama Solaroz</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Desarrollo de una mina de cobre, oro, plata y molibdeno en Catamarca, integrando el yacimiento Agua Rica con la infraestructura existente de Alumbrera, ubicada a unos 35 km. El esquema MARA contempla explotación, procesamiento y uso de instalaciones compartidas para producción destinada principalmente a exportación.</t>
+          <t>Desarrollo integrado de litio en los proyectos Jama y Solaroz, en la Puna de Jujuy, con una planta prevista en el Salar de Jama. La iniciativa contempla extracción de salmuera y producción de compuestos de litio, con una capacidad informada de aproximadamente 22.000 toneladas anuales.</t>
         </is>
       </c>
       <c r="D12">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Glencore (Suiza)</t>
+          <t>CNGR Advanced Material Co., Ltd. (China)</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Minera Agua Rica LLC Sucursal Argentina</t>
+          <t>CNGR Advanced Material Co., Ltd.</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1225,12 +1195,12 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Cobre</t>
+          <t>Litio</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>Catamarca</t>
+          <t>Jujuy</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1239,10 +1209,7 @@
         </is>
       </c>
       <c r="M12">
-        <v>4000</v>
-      </c>
-      <c r="R12">
-        <v>0</v>
+        <v>1151</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
@@ -1250,68 +1217,65 @@
         </is>
       </c>
       <c r="V12" s="2">
-        <v>45887</v>
+        <v>46111</v>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>Globaris; Glencore; Luis Caputo; Reuters; Infobae; auditoría 2026-08-08</t>
+          <t>Globaris; Gobierno de Jujuy; El Tribuno de Jujuy; Infobae; auditoría 2026-08-08</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>https://www.glencore.com/media-and-insights/news/glencore-submits-RIGI-applications-in-respect-of-its-argentine-copper-projects; https://x.com/LuisCaputoAR/status/1957458679835594969; https://www.reuters.com/latam/negocio/7X5ZW2SXG5IYNBUILMTT6GMS6U-2025-08-21/; https://www.infobae.com/economia/2026/05/13/el-gobierno-aprobo-el-ingreso-al-rigi-de-la-ampliacion-del-gasoducto-perito-moreno-con-una-inversion-de-usd-550-millones/</t>
+          <t>https://prensa.jujuy.gob.ar/jujuy/jujuy-se-afianza-como-productor-minerales-criticos-el-desarrollo-la-transicion-energetica-n120116; https://eltribunodejujuy.com/informacion-general/2026-4-1-0-0-0-proyecto-de-litio-en-jujuy-busca-la-adhesion-al-rigi; https://www.infobae.com/economia/2026/05/13/el-gobierno-aprobo-el-ingreso-al-rigi-de-la-ampliacion-del-gasoducto-perito-moreno-con-una-inversion-de-usd-550-millones/</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Jama Solaroz</t>
+          <t>LLL Oil</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Desarrollo integrado de litio en los proyectos Jama y Solaroz, en la Puna de Jujuy, con una planta prevista en el Salar de Jama. La iniciativa contempla extracción de salmuera y producción de compuestos de litio, con una capacidad informada de aproximadamente 22.000 toneladas anuales.</t>
+          <t>Desarrollo integrado de cinco bloques contiguos de petróleo no convencional en Vaca Muerta: La Angostura Norte, La Angostura Sur I, La Angostura Sur II, La Angostura Suroeste y Barreal Grande. El programa prevé perforar 1.152 pozos y compartir instalaciones de superficie y servicios para alcanzar una producción aproximada de 240.000 barriles diarios hacia 2032, destinada a exportación.</t>
         </is>
       </c>
       <c r="D13">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>CNGR Advanced Material Co., Ltd. (China)</t>
+          <t>YPF S.A. (Argentina)</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>CNGR Advanced Material Co., Ltd.</t>
+          <t>YPF</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Minería</t>
+          <t>Petróleo y Gas</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Litio</t>
+          <t>Upstream</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>Jujuy</t>
+          <t>Neuquén</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>NOA</t>
+          <t>Patagonia</t>
         </is>
       </c>
       <c r="M13">
-        <v>1151</v>
-      </c>
-      <c r="R13">
-        <v>0</v>
+        <v>25000</v>
       </c>
       <c r="S13" t="inlineStr">
         <is>
@@ -1319,41 +1283,41 @@
         </is>
       </c>
       <c r="V13" s="2">
-        <v>46111</v>
+        <v>46157</v>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>Globaris; Gobierno de Jujuy; El Tribuno de Jujuy; Infobae; auditoría 2026-08-08</t>
+          <t>Globaris; YPF; EconoJournal; Reuters; auditoría 2026-08-08</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>https://prensa.jujuy.gob.ar/jujuy/jujuy-se-afianza-como-productor-minerales-criticos-el-desarrollo-la-transicion-energetica-n120116; https://eltribunodejujuy.com/informacion-general/2026-4-1-0-0-0-proyecto-de-litio-en-jujuy-busca-la-adhesion-al-rigi; https://www.infobae.com/economia/2026/05/13/el-gobierno-aprobo-el-ingreso-al-rigi-de-la-ampliacion-del-gasoducto-perito-moreno-con-una-inversion-de-usd-550-millones/</t>
+          <t>https://www.instagram.com/p/DYX1JXjj-bC/; https://econojournal.com.ar/destacada/ypf-presento-rigi-acelerar-produccion-petroleo-vaca-muerta/; https://www.reuters.com/business/energy/argentinas-ypf-registers-25-bln-oil-project-rigi-investment-scheme-2026-05-15/</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>LLL Oil</t>
+          <t>Bandurria Norte</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Desarrollo integrado de cinco bloques contiguos de petróleo no convencional en Vaca Muerta: La Angostura Norte, La Angostura Sur I, La Angostura Sur II, La Angostura Suroeste y Barreal Grande. El programa prevé perforar 1.152 pozos y compartir instalaciones de superficie y servicios para alcanzar una producción aproximada de 240.000 barriles diarios hacia 2032, destinada a exportación.</t>
+          <t>Desarrollo greenfield de petróleo no convencional en Bandurria Norte, Vaca Muerta, sobre una superficie aproximada de 26.500 acres. El plan contempla 332 pozos horizontales, planta de tratamiento de crudo, compresión de gas, redes de recolección y ductos, con una meta de 50.000 barriles equivalentes diarios.</t>
         </is>
       </c>
       <c r="D14">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>YPF S.A. (Argentina)</t>
+          <t>Vista Energy (Argentina)</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>YPF</t>
+          <t>Vista Energy</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1377,10 +1341,7 @@
         </is>
       </c>
       <c r="M14">
-        <v>25000</v>
-      </c>
-      <c r="R14">
-        <v>0</v>
+        <v>5800</v>
       </c>
       <c r="S14" t="inlineStr">
         <is>
@@ -1388,41 +1349,41 @@
         </is>
       </c>
       <c r="V14" s="2">
-        <v>46157</v>
+        <v>46224</v>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>Globaris; YPF; EconoJournal; Reuters; auditoría 2026-08-08</t>
+          <t>Globaris; EconoJournal; Vista Energy / SEC; Oil &amp; Gas Journal; auditoría 2026-08-08</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DYX1JXjj-bC/; https://econojournal.com.ar/destacada/ypf-presento-rigi-acelerar-produccion-petroleo-vaca-muerta/; https://www.reuters.com/business/energy/argentinas-ypf-registers-25-bln-oil-project-rigi-investment-scheme-2026-05-15/</t>
+          <t>https://econojournal.com.ar/oilgas/vista-energy-pidio-la-adhesion-al-rigi-para-un-proyecto-de-us-5-800-millones-en-vaca-muerta/; https://www.sec.gov/Archives/edgar/data/1762506/000119312526306139/d151775dex1.htm; https://www.ogj.com/exploration-development/news/55394130/vista-seeks-rigi-approval-for-58-billion-bandurria-norte-development</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Bandurria Norte</t>
+          <t>Argentina LNG</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Desarrollo greenfield de petróleo no convencional en Bandurria Norte, Vaca Muerta, sobre una superficie aproximada de 26.500 acres. El plan contempla 332 pozos horizontales, planta de tratamiento de crudo, compresión de gas, redes de recolección y ductos, con una meta de 50.000 barriles equivalentes diarios.</t>
+          <t>Proyecto integrado de producción y exportación de gas natural licuado: desarrollo de gas rico en Vaca Muerta, infraestructura dedicada de transporte, plantas de procesamiento y fraccionamiento y dos unidades flotantes de licuefacción (FLNG) por 12 MTPA en el Golfo San Matías.</t>
         </is>
       </c>
       <c r="D15">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Vista Energy (Argentina)</t>
+          <t>YPF S.A. (Argentina); Eni S.p.A. (Italia); XRG (Emiratos Árabes Unidos)</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vista Energy</t>
+          <t>YPF</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1432,12 +1393,12 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Upstream</t>
+          <t>Midstream</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>Neuquén</t>
+          <t>Neuquén; Río Negro</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -1446,10 +1407,7 @@
         </is>
       </c>
       <c r="M15">
-        <v>5800</v>
-      </c>
-      <c r="R15">
-        <v>0</v>
+        <v>51000</v>
       </c>
       <c r="S15" t="inlineStr">
         <is>
@@ -1457,41 +1415,36 @@
         </is>
       </c>
       <c r="V15" s="2">
-        <v>46224</v>
+        <v>46247</v>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>Globaris; EconoJournal; Vista Energy / SEC; Oil &amp; Gas Journal; auditoría 2026-08-08</t>
+          <t>YPF / Argentina LNG; La Nación; Infobae; Data Energía</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>https://econojournal.com.ar/oilgas/vista-energy-pidio-la-adhesion-al-rigi-para-un-proyecto-de-us-5-800-millones-en-vaca-muerta/; https://www.sec.gov/Archives/edgar/data/1762506/000119312526306139/d151775dex1.htm; https://www.ogj.com/exploration-development/news/55394130/vista-seeks-rigi-approval-for-58-billion-bandurria-norte-development</t>
+          <t>https://argentina-lng.ypf.com/assets/pdf/ENG-Argentina-LNG-Adhesion-RIGI.pdf; https://www.lanacion.com.ar/economia/un-proyecto-por-us51000-millones-impulsado-por-ypf-solicito-la-adhesion-al-rigi-nid13082026/; https://www.infobae.com/economia/2026/08/13/con-una-inversion-de-usd-50000-millones-ypf-presenta-al-rigi-el-mayor-proyecto-de-su-historia-para-exportar-gas-de-vaca-muerta/; https://dataenergia.ar/gas/argentina-lgn-solicitaron-la-adhesion-formal-al-rigi-para-una-inversion-historica-de-u-s-51-000-millones-202681319370</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Argentina LNG</t>
+          <t>PAE Cerro Dragón</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Proyecto integrado de producción y exportación de gas natural licuado: desarrollo de gas rico en Vaca Muerta, infraestructura dedicada de transporte, plantas de procesamiento y fraccionamiento y dos unidades flotantes de licuefacción (FLNG) por 12 MTPA en el Golfo San Matías.</t>
+          <t>Desarrollo de recuperación terciaria de petróleo convencional en Cerro Dragón: 22 plantas de inyección de polímeros, perforación de 100 pozos productores e inyectores, adecuación de pozos, intervención de otros 600 pozos productores e infraestructura complementaria de superficie. Producción incremental estimada: 46 millones de barriles de petróleo y 30 BCF de gas natural.</t>
         </is>
       </c>
       <c r="D16">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>YPF S.A. (Argentina); Eni S.p.A. (Italia); XRG (Emiratos Árabes Unidos)</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>YPF</t>
+          <t>Pan American Energy (PAE) (Argentina)</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1501,24 +1454,21 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Midstream</t>
+          <t>Upstream</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>Neuquén; Río Negro</t>
+          <t>Chubut</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>Patagonia</t>
+          <t>Área Cerro Dragón, Cuenca del Golfo San Jorge</t>
         </is>
       </c>
       <c r="M16">
-        <v>51000</v>
-      </c>
-      <c r="R16">
-        <v>0</v>
+        <v>1200</v>
       </c>
       <c r="S16" t="inlineStr">
         <is>
@@ -1526,129 +1476,125 @@
         </is>
       </c>
       <c r="V16" s="2">
-        <v>46247</v>
+        <v>46296</v>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>YPF / Argentina LNG; La Nación; Infobae; Data Energía</t>
+          <t>Gobierno del Chubut (01/10/2026); La Nación / PAE (01/10/2026); Reuters / Luis Caputo (01/10/2026)</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>https://argentina-lng.ypf.com/assets/pdf/ENG-Argentina-LNG-Adhesion-RIGI.pdf; https://www.lanacion.com.ar/economia/un-proyecto-por-us51000-millones-impulsado-por-ypf-solicito-la-adhesion-al-rigi-nid13082026/; https://www.infobae.com/economia/2026/08/13/con-una-inversion-de-usd-50000-millones-ypf-presenta-al-rigi-el-mayor-proyecto-de-su-historia-para-exportar-gas-de-vaca-muerta/; https://dataenergia.ar/gas/argentina-lgn-solicitaron-la-adhesion-formal-al-rigi-para-una-inversion-historica-de-u-s-51-000-millones-202681319370</t>
+          <t>https://noticias.chubut.gob.ar/notas/gobierno/5481/torres-encabezo-en-la-sede-de-la-ocde-el-anuncio-de-una-inversion-de-usd-1200-millones-de-pae-para-cerro-dragon.html; https://www.lanacion.com.ar/economia/pan-american-energy-busca-ingresar-al-rigi-con-una-inversion-de-us1200-millones-para-revitalizar-nid01102026/; https://www.reuters.com/business/energy/pae-invest-12-billion-argentina-oil-field-minister-says-2026-10-01/</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>PAE Cerro Dragón</t>
+          <t>Pampa Exploración S.A.</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Desarrollo de recuperación terciaria de petróleo convencional en Cerro Dragón: 22 plantas de inyección de polímeros, perforación de 100 pozos productores e inyectores, adecuación de pozos, intervención de otros 600 pozos productores e infraestructura complementaria de superficie. Producción incremental estimada: 46 millones de barriles de petróleo y 30 BCF de gas natural.</t>
+          <t>Desarrollo del depósito Lunahuasi de cobre, oro y plata, actualmente en exploración, con perforaciones y una galería de exploración planificada para avanzar hacia su desarrollo minero</t>
         </is>
       </c>
       <c r="D17">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Pan American Energy (PAE) (Argentina)</t>
+          <t>NGEx Minerals Ltd. (Canadá)</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Pampa Exploración S.A.</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Petróleo y Gas</t>
+          <t>Minería</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Upstream</t>
+          <t>Cobre</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>Chubut</t>
+          <t>San Juan</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>Área Cerro Dragón, Cuenca del Golfo San Jorge</t>
+          <t>Departamento Iglesia; Distrito Vicuña</t>
         </is>
       </c>
       <c r="M17">
-        <v>1200</v>
+        <v>2437</v>
       </c>
       <c r="S17" t="inlineStr">
         <is>
           <t>En evaluación</t>
         </is>
       </c>
-      <c r="V17" s="2">
-        <v>46296</v>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>Gobierno del Chubut (01/10/2026); La Nación / PAE (01/10/2026); Reuters / Luis Caputo (01/10/2026)</t>
+          <t>NGEx Minerals, 14/05/2026; Panorama Minero, consulta 02/10/2026</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>https://noticias.chubut.gob.ar/notas/gobierno/5481/torres-encabezo-en-la-sede-de-la-ocde-el-anuncio-de-una-inversion-de-usd-1200-millones-de-pae-para-cerro-dragon.html; https://www.lanacion.com.ar/economia/pan-american-energy-busca-ingresar-al-rigi-con-una-inversion-de-us1200-millones-para-revitalizar-nid01102026/; https://www.reuters.com/business/energy/pae-invest-12-billion-argentina-oil-field-minister-says-2026-10-01/</t>
+          <t>https://ngexminerals.com/news/ngex-releases-2025-sustainability-summary-122811/; https://www.panorama-minero.com/es/mining-compendium/argentina/project/lunahuasi</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Pampa Exploración S.A.</t>
+          <t>Procesamiento de NGLs en Tratayén</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Desarrollo del depósito Lunahuasi de cobre, oro y plata, actualmente en exploración, con perforaciones y una galería de exploración planificada para avanzar hacia su desarrollo minero</t>
+          <t>Construcción de un gasoducto de segregación de corrientes de aproximadamente 100 km y nuevas instalaciones de procesamiento en Tratayén, con capacidad para 43 millones de m³ diarios, para separar líquidos del gas natural. Integra un paquete de dos proyectos de TGS con inversión conjunta superior a USD 3.200 millones; el monto actualizado por VPU no fue publicado.</t>
         </is>
       </c>
       <c r="D18">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>NGEx Minerals Ltd. (Canadá)</t>
+          <t>Transportadora de Gas del Sur S.A. (TGS) (Argentina)</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Pampa Exploración S.A.</t>
+          <t>Procesadora de Gas del Sur S.A. (PGS)</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Minería</t>
+          <t>Petróleo y Gas</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Cobre</t>
+          <t>Midstream</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>San Juan</t>
+          <t>Neuquén</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>Departamento Iglesia; Distrito Vicuña</t>
-        </is>
-      </c>
-      <c r="M18">
-        <v>2437</v>
-      </c>
-      <c r="R18">
-        <v>0</v>
+          <t>Tratayén, Neuquén</t>
+        </is>
       </c>
       <c r="S18" t="inlineStr">
         <is>
@@ -1657,28 +1603,28 @@
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>NGEx Minerals, 14/05/2026; Panorama Minero, consulta 02/10/2026</t>
+          <t>Luis Caputo / Ministerio de Economía (X, 19/10/2026); Shale24 (19/10/2026); TGS, estados financieros 2T 2026 (04/08/2026)</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>https://ngexminerals.com/news/ngex-releases-2025-sustainability-summary-122811/; https://www.panorama-minero.com/es/mining-compendium/argentina/project/lunahuasi</t>
+          <t>https://x.com/LuisCaputoAR/status/2112170371310858454; https://www.shale24.com/oil-gas/tgs-entra-rigi-us-3200-millones-bahia-blanca-ya-suma-dos-obras-liquidos-vaca-muerta-regimen-n1864; https://api.mziq.com/mzfilemanager/v2/d/78ce1f91-b610-429f-b020-add32c211c1f/dcfe21a3-8a28-44d7-5aeb-2e1a49a861e2?origin=2</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Procesamiento de NGLs en Tratayén</t>
+          <t>Poliducto Tratayén–Bahía Blanca y complejo NGL Puerto Galván</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Construcción de un gasoducto de segregación de corrientes de aproximadamente 100 km y nuevas instalaciones de procesamiento en Tratayén, con capacidad para 43 millones de m³ diarios, para separar líquidos del gas natural. Integra un paquete de dos proyectos de TGS con inversión conjunta superior a USD 3.200 millones; el monto actualizado por VPU no fue publicado.</t>
+          <t>Construcción de un poliducto de 577 km desde Tratayén hasta Bahía Blanca, una planta de fraccionamiento, instalaciones de almacenamiento y obras en la terminal marítima de Puerto Galván para exportar aproximadamente 2,7 millones de toneladas anuales de propano, butano y gasolina natural. Integra un paquete de dos proyectos de TGS con inversión conjunta superior a USD 3.200 millones; el monto actualizado por VPU no fue publicado.</t>
         </is>
       </c>
       <c r="D19">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -1687,7 +1633,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Procesadora de Gas del Sur S.A. (PGS)</t>
+          <t>Midstream de Gas del Sur S.A. (MGS)</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1702,16 +1648,13 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>Neuquén</t>
+          <t>Neuquén; Buenos Aires</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>Tratayén, Neuquén</t>
-        </is>
-      </c>
-      <c r="R19">
-        <v>0</v>
+          <t>Tratayén–Bahía Blanca / Puerto Galván</t>
+        </is>
       </c>
       <c r="S19" t="inlineStr">
         <is>
@@ -1724,69 +1667,6 @@
         </is>
       </c>
       <c r="AB19" t="inlineStr">
-        <is>
-          <t>https://x.com/LuisCaputoAR/status/2112170371310858454; https://www.shale24.com/oil-gas/tgs-entra-rigi-us-3200-millones-bahia-blanca-ya-suma-dos-obras-liquidos-vaca-muerta-regimen-n1864; https://api.mziq.com/mzfilemanager/v2/d/78ce1f91-b610-429f-b020-add32c211c1f/dcfe21a3-8a28-44d7-5aeb-2e1a49a861e2?origin=2</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Poliducto Tratayén–Bahía Blanca y complejo NGL Puerto Galván</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Construcción de un poliducto de 577 km desde Tratayén hasta Bahía Blanca, una planta de fraccionamiento, instalaciones de almacenamiento y obras en la terminal marítima de Puerto Galván para exportar aproximadamente 2,7 millones de toneladas anuales de propano, butano y gasolina natural. Integra un paquete de dos proyectos de TGS con inversión conjunta superior a USD 3.200 millones; el monto actualizado por VPU no fue publicado.</t>
-        </is>
-      </c>
-      <c r="D20">
-        <v>46</v>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>Transportadora de Gas del Sur S.A. (TGS) (Argentina)</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>Midstream de Gas del Sur S.A. (MGS)</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>Petróleo y Gas</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>Midstream</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>Neuquén; Buenos Aires</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>Tratayén–Bahía Blanca / Puerto Galván</t>
-        </is>
-      </c>
-      <c r="R20">
-        <v>0</v>
-      </c>
-      <c r="S20" t="inlineStr">
-        <is>
-          <t>En evaluación</t>
-        </is>
-      </c>
-      <c r="AA20" t="inlineStr">
-        <is>
-          <t>Luis Caputo / Ministerio de Economía (X, 19/10/2026); Shale24 (19/10/2026); TGS, estados financieros 2T 2026 (04/08/2026)</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
         <is>
           <t>https://x.com/LuisCaputoAR/status/2112170371310858454; https://www.shale24.com/oil-gas/tgs-entra-rigi-us-3200-millones-bahia-blanca-ya-suma-dos-obras-liquidos-vaca-muerta-regimen-n1864; https://api.mziq.com/mzfilemanager/v2/d/78ce1f91-b610-429f-b020-add32c211c1f/dcfe21a3-8a28-44d7-5aeb-2e1a49a861e2?origin=2</t>
         </is>
